--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -6857,7 +6857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -7058,7 +7058,11 @@
           <t>WholesaleTypePredict2Param</t>
         </is>
       </c>
-      <c r="AJ2" s="7" t="n"/>
+      <c r="AJ2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -12689,6 +12693,1956 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>не опт</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1443270089</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Сосна кругляк лесовоз(ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Братск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под сосна кругляк лесовоз. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Братск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_03.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Иркутская область, Братск</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>2026-08-14T14:33:49+03:00</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:33:49+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3187889362</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Лиственница пиловочник(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Усть-Илимск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под лиственница пиловочник. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Усть-Илимск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Иркутская область, Усть-Илимск</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>2026-07-16T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6255946758</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ель кругляк хвоя(документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Усинск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под ель кругляк хвоя. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Усинск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_03.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Республика Коми, Усинск</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4808340791</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Пихта кругляк лес(QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ухта и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под пихта кругляк лес. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Ухта и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Республика Коми, Ухта</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>2026-08-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>2026-07-16T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1228193305</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Берёза кругляк дрова(ЭСД на рейс)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Котлас и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под берёза кругляк дрова. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Котлас и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_03.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Архангельская область, Котлас</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>2026-08-15T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>2026-07-16T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5796638201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Кедр пиловочник(документы и учёт ФГИС)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Сыктывкар и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под кедр пиловочник. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Сыктывкар и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_03.jpg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Республика Коми, Сыктывкар</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>2026-08-15T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1138895139</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(ЭСД и QR код)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Канск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под хвоя кругляк оптом. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Канск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Красноярский край, Канск</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>2026-08-15T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6633662431</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник(лесная декларация ФГИС)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Лесосибирск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под сосна пиловочник. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Лесосибирск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_03.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Красноярский край, Лесосибирск</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>2026-08-15T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>2026-07-16T20:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1028057845</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк(документы на лес ФГИС)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Шарыпово и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под лиственница кругляк. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Шарыпово и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_03.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Красноярский край, Шарыпово</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>2026-08-16T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>2026-07-17T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3171758646</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ель сосна кругляк(QR код на вывозку)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Асино и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под ель сосна кругляк. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Асино и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_03.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Томская область, Асино</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>2026-07-17T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9006113370</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Осина кругляк дрова(ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Нягань и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под осина кругляк дрова. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Нягань и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_03.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Нягань</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>2026-08-16T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>2026-07-17T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2922023278</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Берёза пиловочник(QR код и документы ФГИС)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Югорск и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под берёза пиловочник. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Югорск и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_03.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО, Югорск</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>2026-08-16T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2020162379</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Сосна кругляк на корню(ЭСД и учёт)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Кудымкар и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под сосна кругляк на корню. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Кудымкар и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_03.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Пермский край, Кудымкар</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>2026-08-16T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6166594362</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Хвоя лиственница лес(документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Урень и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под хвоя лиственница лес. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Урень и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_03.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Нижегородская область, Урень</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>2026-08-16T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>2026-07-17T17:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2048065568</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Кедр кругляк деловой(QR код на рейс)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Колпашево и район, помогаю с документами на лес под ключ. Делаю куар код на перевозку и электронную накладную ЭСД из ФГИС ЛК, каждая машина едет с готовым документом, на посту и проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Беру на себя лесную декларацию, отчёт использования лесов, закрытие расхождений по объёмам и подбор кодов ОКПД2 под кедр кругляк деловой. Оформляю быстро, за пятнадцать минут, работаю с ИП и ООО.&lt;br&gt;&lt;br&gt;Для оформления нужно немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Остальное беру на себя.&lt;br&gt;&lt;br&gt;Пишите или звоните, гляну вашу ситуацию по Колпашево и скажу, какие бумаги нужны и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_03.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Томская область, Колпашево</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>2026-08-16T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>2026-07-17T20:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_03.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_03.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_03.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_03.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_00.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -2541,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -2651,7 +2651,11 @@
           <t>CompanyName</t>
         </is>
       </c>
-      <c r="T2" s="7" t="n"/>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -3908,6 +3912,261 @@
       <c r="S16" t="inlineStr">
         <is>
           <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7504069999</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_3.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>350</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник на распил(документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>На пилораму заходит сосна с нескольких делянок, машины разгружают, доска уже уехала заказчику, а в системе приёмка не проведена и остаток по складу висит не тот. &lt;br&gt; &lt;br&gt; Ведём весь цикл документов у переработчика: проводим входящий лес, оформляем ЭСД это электронный сопроводительный документ на перевозку древесины, ведём МСД это материально-складской документ по цеху, сводим объём распиленного сырья с выходом продукции, готовим ОЛИ это отчёт об использовании лесов и закрываем расхождения по кубам, если приход и расход разошлись. Всё идёт через ФГИС ЛК это государственная система учёта древесины. &lt;br&gt; &lt;br&gt; Порядок работы: &lt;br&gt; 1. Присылаете реквизиты предприятия, данные по площадке приёмки и остаток по складу на сегодня. &lt;br&gt; 2. Скидываете входящие документы на партии сосны и накладные на отгрузку пиломатериала. &lt;br&gt; 3. Получаете проведённую приёмку, ровный склад в системе и готовый документ на каждый рейс с QR кодом. &lt;br&gt; &lt;br&gt; На один рейс уходит около пятнадцати минут, полный разбор склада с расхождениями обычно занимает рабочий день. &lt;br&gt; &lt;br&gt; Документы настоящие, формируются в государственной системе от лица вашей организации. На посту и на весовой такой QR код проверяется и вопросов не вызывает, работаем только штатным порядком учёта. &lt;br&gt; &lt;br&gt; Напишите или позвоните, посмотрим ваш склад и скажем, что нужно поправить.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Вологда, ул. Мира, 6</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-08-20T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6186451618</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_3.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>400</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ель пиловочник(МСД и складской учёт)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>На складе пиломатериалов обычно так: приняли вагон еловой доски, часть ушла в распил, часть отгрузили, а по бумагам остаток живёт своей жизнью. Через месяц кладовщик пересчитывает штабеля по факту, а в системе цифры другие, и отгружать уже боязно.&lt;br&gt; &lt;br&gt;Ведём складской учёт древесины и оформляем МСД, это материально-складской документ. Он показывает, сколько древесины поступило на площадку, сколько ушло в переработку и сколько отгружено. Всё проводится в ФГИС ЛК, это государственная система учёта древесины. Под отгрузку готовим ЭСД, это электронный сопроводительный документ на перевозку древесины, с QR кодом на рейс.&lt;br&gt; &lt;br&gt;Как это идёт по шагам:&lt;br&gt;1. Присылаете реквизиты, данные по площадке и приходные документы на ту ель, что уже лежит на складе.&lt;br&gt;2. Сверяем фактический остаток с тем, что числится в системе, и показываем, где именно разошлось.&lt;br&gt;3. Заводим склад, проводим приход, переработку и отгрузку, оформляем МСД. Если нужно, сдаём ОЛИ, это отчёт об использовании лесов.&lt;br&gt;4. Получаете готовые документы и понятный остаток по складу.&lt;br&gt; &lt;br&gt;По срокам: если бумаги на руках, укладываемся от пары часов до одного рабочего дня. Постановка склада с нуля идёт дольше, зависит от объёма и того, насколько запущен учёт.&lt;br&gt; &lt;br&gt;Документы настоящие, оформляются от вашего имени в государственной системе, проверку на посту и на весовой проходят. Всё ведём штатным порядком, как требует регламент.&lt;br&gt; &lt;br&gt;Напишите или позвоните, посмотрим вашу ситуацию по складу и скажем, что реально сделать.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Костромская обл., Кострома, ул. Советская, 8</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-07-23T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4185478225</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_3.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>350</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Берёза кругляк(объёмы по бумагам и по факту)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>На площадке приняли берёзу, обмерили по факту, а в бумагах объём другой. Кто-то считал в плотных кубах, кто-то в складочных, часть ушла в отсев по гнили, и по документам выходит больше, чем реально лежит у цеха. Пока цифры не сведены, следующую отгрузку оформить не получится.&lt;br&gt; &lt;br&gt;Занимаюсь именно этим: привожу учёт в ФГИС ЛК, это государственная система учёта древесины, в соответствие с фактом на площадке. Разбираю, где разошлось: приход, списание в распиловку, остаток на складе. Правлю МСД, это материально-складской документ, и ОЛИ, отчёт об использовании лесов, если расхождение тянется ещё с делянки. После этого на отгрузку выпускается ЭСД, электронный сопроводительный документ на перевозку древесины, с QR-кодом.&lt;br&gt; &lt;br&gt;Как идёт работа:&lt;br&gt;1. Присылаете выгрузку приходов и остатков из системы или доступ к ней, плюс свои замеры по факту.&lt;br&gt;2. Показываю, где сидит разница и на какой операции она появилась.&lt;br&gt;3. Получаете сведённый остаток, исправленные документы и возможность оформлять новые рейсы.&lt;br&gt; &lt;br&gt;Обычно занимает от нескольких часов до одного рабочего дня. Если операций много, скажу об этом сразу, а не по ходу дела.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, обходных путей тут нет. Документы настоящие, на посту и на весовой проверка проходит штатно.&lt;br&gt; &lt;br&gt;Напишите или позвоните, посмотрим ваши цифры и станет понятно, откуда взялась разница.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Кировская обл., Киров, ул. Ленина, 85</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-08-23T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-07-24T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -4453,7 +4712,11 @@
           <t>AvitoDateEnd</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="n"/>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -6205,6 +6468,381 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-05T10:10:53+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1552592490</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_3.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>300</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Сосна кругляк первый рейс(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Первая отгрузка обычно выглядит так: лесовоз загружен, водитель ждёт, а бумаг на рейс нет, потому что раньше лес возили внутри своей делянки и вопрос не вставал. Разбираем всё по шагам, чтобы вы поняли порядок и дальше делали это сами.&lt;br&gt; &lt;br&gt;Оформляем ЭСД, это электронный сопроводительный документ на перевозку древесины, и QR код к нему. Всё проходит через ФГИС ЛК, государственную систему учёта древесины. При необходимости поправим остатки, чтобы объём в системе сошёлся с тем, что реально лежит на площадке.&lt;br&gt; &lt;br&gt;Порядок работы простой.&lt;br&gt;1. Присылаете реквизиты отправителя и получателя, породу, сортимент и объём по кубам.&lt;br&gt;2. Добавляете данные машины и водителя, а также точки погрузки и выгрузки.&lt;br&gt;3. Показываете основание на древесину: договор, декларацию или сделку в системе.&lt;br&gt;4. Получаете готовый ЭСД и QR код в электронном виде, распечатать может сам водитель.&lt;br&gt; &lt;br&gt;По срокам: обычная перевозка оформляется в течение часа после того, как пришли данные. Если рейс горит, скажите об этом сразу, сделаем вне очереди.&lt;br&gt; &lt;br&gt;Документ настоящий и числится в государственной системе, поэтому на посту и на весовой он спокойно проверяется по коду. Оформляем строго по штатному порядку учёта древесины.&lt;br&gt; &lt;br&gt;Работаем по всей области и соседним регионам, ехать никуда не нужно. Если возите лес впервые и не понимаете, с чего начать, напишите или позвоните, объясним нормальным языком и поможем с первым рейсом.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Смоленск, ул. Николаева, 12</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5569767896</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_3.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>400</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Берёза кругляк(лесная декларация и ОЛИ в срок)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Знакомая история: делянка отведена, техника уже в лесу, а лесная декларация не подана или подана с ошибкой в породах и объёмах. Рубить нельзя, простой идёт, а срок сдачи отчётности подходит вплотную.&lt;br&gt; &lt;br&gt;Занимаемся этим каждый день. Подаём лесную декларацию через ФГИС ЛК, это государственная система учёта древесины, и дальше ведём по ней отчётность. ОЛИ это отчёт об использовании лесов, его сдают в установленный срок после отчётного периода. Если параллельно идёт вывозка, оформляем ЭСД, электронный сопроводительный документ на перевозку древесины, и закрываем МСД, материально-складской документ по складу.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Вы присылаете договор аренды или купли-продажи, проект освоения лесов и данные по делянке.&lt;br&gt;2. Мы считаем объёмы по породам и сортиментам и сверяем их с тем, что уже стоит в системе.&lt;br&gt;3. Вы получаете поданную от вашего юрлица декларацию и отчёт с квитанцией о приёме, всё это видно в вашем личном кабинете.&lt;br&gt; &lt;br&gt;Обычный срок один рабочий день, по декларации на новую делянку до двух. Если сегодня последний день подачи, скажите сразу, возьмём вне очереди.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документы настоящие. ЭСД проходит проверку на посту и на весовой, вопросов у инспектора не возникает.&lt;br&gt; &lt;br&gt;Напишите или позвоните, посмотрим ваши сроки и сразу скажем, что успеваем закрыть.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Республика Марий Эл, Йошкар-Ола, ул. Советская, 173</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026-07-25T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7842661941</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_3.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>300</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ель кругляк(документы ФГИС ЛК удалённо)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>На делянке редко есть бухгалтер, а часто нет и человека, который сидит за компьютером. Лесовоз загружен, водитель ждёт, а документа на рейс нет, потому что оформлять его некому. Разбираем как раз такие случаи: вы работаете в лесу, а учёт и оформление ведём за вас удалённо.&lt;br&gt; &lt;br&gt;Работаем в ФГИС ЛК, это государственная система учёта древесины. Оформляем ЭСД, электронный сопроводительный документ на перевозку древесины, с QR кодом на каждый рейс. Ведём МСД, материально-складской документ по складу и делянке. Готовим ОЛИ, отчёт об использовании лесов, и лесные декларации. Если объёмы в системе разошлись с фактом на делянке, сводим их и приводим остатки в порядок.&lt;br&gt; &lt;br&gt;Как это устроено:&lt;br&gt;1. Присылаете данные по делянке: договор или декларацию, объём, породу, сортимент.&lt;br&gt;2. Пишете, куда и на чём идёт машина: номер лесовоза, водитель, получатель.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водителю остаётся показать его при проверке.&lt;br&gt; &lt;br&gt;По срокам: рейсовый документ обычно готов в течение часа после ваших данных, отчёты и декларации от одного дня.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему от вашего юрлица или ИП, доступ настраиваем вместе с вами. Документ настоящий, на посту и на весовой сканируется по QR коду и проходит проверку.&lt;br&gt; &lt;br&gt;Если делянка есть, а вести документы некому, напишите или позвоните. Посмотрим вашу ситуацию и скажем, что нужно сделать в первую очередь.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Республика Коми, Вуктыл, ул. Комсомольская, 14</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-24T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2026-07-25T15:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -6857,7 +7495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -14643,6 +15281,1770 @@
       <c r="AJ58" t="inlineStr">
         <is>
           <t>2026-07-17T20:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9582797849</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник(QR код и ЭСД до выезда)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Знакомая картина: лесовоз с сосновым пиловочником остановили на посту, груз есть, а документа на перевозку водитель показать не может. Машина стоит, время идёт, на площадке приёмки её уже ждут.&lt;br&gt; &lt;br&gt;Мы оформляем документы на древесину через ФГИС ЛК, это государственная система учёта древесины. Выпускаем ЭСД, электронный сопроводительный документ на перевозку древесины, и QR код к нему, который инспектор считывает телефоном прямо у обочины.&lt;br&gt; &lt;br&gt;Как это проходит:&lt;br&gt;1. Присылаете данные по рейсу: порода, сортимент, объём, откуда и куда идёт машина.&lt;br&gt;2. Добавляете сведения о перевозчике и автомобиле, реквизиты отправителя и получателя.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водителю достаточно открыть его в телефоне или показать распечатку.&lt;br&gt; &lt;br&gt;По срокам: когда данные пришли полные, готовый документ выпускаем за пятнадцать, двадцать минут. Отвечаем и в выходные, машины ходят не по графику офиса.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий и числится в базе. На посту и на весовой проверку проходит, у приёмщика вопросов по бумагам не остаётся.&lt;br&gt; &lt;br&gt;Если сосна уходит с площадки регулярно, ведём рейсы постоянно, а вместе с этим сводим расхождения объёмов, готовим МСД, материально-складской документ, и ОЛИ, отчёт об использовании лесов.&lt;br&gt; &lt;br&gt;Напишите или позвоните, разберём вашу ситуацию по рейсу и скажем, каких данных не хватает для документа.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_3.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Калужская обл., Калуга, ул. Кирова, 1</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>2026-08-20T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4400874571</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник дрова(QR код на лесовоз)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Машина загрузилась, доехала до поста, а предъявить нечего. Лесовоз ставят в сторону, приёмка ждёт, водитель звонит каждые десять минут. Чаще всего так выходит у тех, кто возит первый сезон и ещё не разобрался, как оформляется рейс с лесом и пиломатериалом.&lt;br&gt; &lt;br&gt;Работаем в ФГИС ЛК, это государственная система учёта древесины. Делаем ЭСД, это электронный сопроводительный документ на перевозку древесины, и выдаём к нему QR код на рейс. Объясняем по ходу простыми словами, без терминов, которые ничего не проясняют.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Присылаете, что везёте: порода, сортимент или размер пиломатериала, объём в кубах, откуда и куда идёт машина.&lt;br&gt;2. Добавляете перевозчика: марка и номер тягача, прицеп, фамилия водителя.&lt;br&gt;3. Сообщаете, на каком основании у вас древесина: договор купли-продажи, лесная декларация, сделка в системе. Если не понимаете, что из этого у вас есть, пришлите фото бумаг, разберёмся сами и скажем прямо.&lt;br&gt;4. Получаете готовый ЭСД с QR кодом файлом и ссылкой. Водителю хватит показать код с телефона.&lt;br&gt; &lt;br&gt;По времени обычно от пятнадцати минут до часа в рабочие часы. Про ночной рейс скажите заранее, подстроимся.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий и числится за вашей организацией. На посту и на весовой он проверяется по коду и вопросов не вызывает. Дальше при необходимости ведём МСД, это материально-складской документ, и ОЛИ, это отчёт об использовании лесов, чтобы объёмы сходились.&lt;br&gt; &lt;br&gt;Напишите или позвоните, посмотрим вашу ситуацию и подскажем, что нужно.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Брянская обл., Клинцы, ул. Октябрьская, 28</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>2026-08-20T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6593893298</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Берёза пиловочник(документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Сам веду документы по лесу уже несколько лет, поэтому хорошо знаю, где обычно всё встаёт. Приезжает машина под берёзовый пиловочник, на пилораме уже готовы доска и заготовка, покупатель ждёт, а в системе объём не проведён и отгружать нечего. Такие ситуации разбираю почти каждый день.&lt;br&gt; &lt;br&gt;Работаю в ФГИС ЛК, это государственная система учёта древесины. Оформляю ЭСД, электронный сопроводительный документ на перевозку древесины, с QR кодом на рейс, веду МСД, материально-складской документ по складу и пилораме, готовлю ОЛИ, отчёт об использовании лесов, и свожу объёмы, если приход и расход разошлись.&lt;br&gt; &lt;br&gt;По шагам это выглядит так:&lt;br&gt;1. Присылаете породу, объём, откуда и куда идёт машина, данные перевозчика и получателя.&lt;br&gt;2. Я смотрю остатки в системе и сразу говорю, чего не хватает, до начала оформления.&lt;br&gt;3. Провожу операцию и возвращаю готовый документ с QR кодом, водителю достаточно показать его с телефона или на распечатке.&lt;br&gt; &lt;br&gt;По срокам: рейс обычно оформляю в течение часа после получения данных, отчёты и сведение объёмов занимают от одного дня, зависит от того, насколько запущен учёт.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, под вашей организацией и по вашим документам. Документ настоящий, на посту и на весовой проверяется по QR коду и вопросов не вызывает.&lt;br&gt; &lt;br&gt;Напишите или позвоните, посмотрю вашу ситуацию и скажу, что реально сделать и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Вязьма, ул. Ленина, 77</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2026-07-22T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3141895047</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник на переработку(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Карелия, лесовоз загружен и идёт на переработку, а на приёмке выясняется, что документа на рейс нет или он оформлен не на тот объём. Машина стоит, водитель ждёт, склад ждёт. Обычно это чинится за то время, пока водитель курит у кабины.&lt;br&gt; &lt;br&gt;Делаем документы на вывозку сосны и другой хвои с делянки, с промежуточного склада и на завод. ЭСД это электронный сопроводительный документ на перевозку древесины, оформляем его в ФГИС ЛК, государственной системе учёта древесины, и к нему сразу выходит QR код, который проверяют на дороге. Заодно приводим в порядок остальное: МСД это материально-складской документ по складу, ОЛИ это отчёт об использовании лесов, лесные декларации, а также сводим объёмы, если по остаткам разошлось.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Присылаете данные рейса: порода, объём, откуда и куда идёт машина, госномер и данные водителя.&lt;br&gt;2. Присылаете реквизиты отправителя и получателя, а также основание на древесину.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водитель показывает его с телефона или на распечатке.&lt;br&gt; &lt;br&gt;По срокам: обычный рейс оформляем за 15 минут, редко дольше получаса, если данные приходят кусками. Работаем и в выходные, лес возят не по графику.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий, на посту и на весовой проверку проходит, у получателя он принимается штатно.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите откуда и куда идёт машина и какой объём, подскажем что нужно именно по вашему рейсу.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Суоярви, ул. Ленина, 33</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2817788089</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Кедр пиловочник зимник(QR код на вывозку)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Зимник встал, машины пошли одна за другой, а к весне дорога поплыла и вывозка идёт рывками. В такие недели чаще всего и всплывает, что на очередной рейс кедрового пиловочника нет действующего документа, водитель стоит на выезде с делянки и ждёт.&lt;br&gt; &lt;br&gt;Помогаем оформить ЭСД, это электронный сопроводительный документ на перевозку древесины, и QR код к нему на каждый рейс. Работаем в ФГИС ЛК, это государственная система учёта древесины. Заодно ведём МСД, это материально-складской документ по площадке, и готовим ОЛИ, это отчёт об использовании лесов, чтобы к концу сезона объёмы по вывозке и по остатку сошлись.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Присылаете реквизиты, данные по отводу или по площадке и объём партии.&lt;br&gt;2. Сообщаете породу, сортимент, номер машины и маршрут по каждому рейсу.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водитель показывает его с телефона или везёт распечатку.&lt;br&gt; &lt;br&gt;Обычный рейс закрываем в течение часа в рабочее время, срочные рейсы по зимнику оформляем и раньше, если данные пришли полностью. По межсезонью удобно сразу отдать список машин на неделю, тогда документы готовим по мере выхода.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий и числится за вашей организацией. На посту и на весовой такой QR код проверяется и вопросов не вызывает.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите объём и когда идёт первая машина, посмотрим по вашей ситуации.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Томская обл., Каргасок, ул. Пушкина, 31</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Кедр</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>2026-08-21T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3465344029</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс(ЭСД на каждую машину)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Дрова и берёзовый баланс редко едут фурами. Обычно это одна машина сегодня до котельной, завтра один рейс на приёмку сырья, послезавтра ещё пара ходок с делянки. Объёмы мелкие, документ нужен на каждый выезд, и на посту короткий рейс никого не оправдывает.&lt;br&gt; &lt;br&gt;Оформляем ЭСД, это электронный сопроводительный документ на перевозку древесины, отдельно под каждый рейс. Делается это в ФГИС ЛК, это государственная система учёта древесины. Попутно приводим в порядок МСД, это материально-складской документ по вашему складу, и ОЛИ, это отчёт об использовании лесов, если по ним накопились хвосты.&lt;br&gt; &lt;br&gt;Как проходит работа:&lt;br&gt;1. Присылаете данные отправителя и получателя, породу, сортимент и объём по рейсу.&lt;br&gt;2. Добавляете марку и номер машины, фамилию водителя, точку погрузки и точку выгрузки.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водитель показывает его с телефона или везёт распечатку.&lt;br&gt; &lt;br&gt;Один рейс оформляется примерно за пятнадцать минут в рабочее время. Если машин за день несколько, ставим их в очередь и закрываем подряд, созваниваться по каждой отдельно не нужно.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему учёта, документ настоящий и числится в базе. На посту и на весовой его проверяют сканированием QR кода, вопросов он не вызывает.&lt;br&gt; &lt;br&gt;Если возите берёзовые дрова и баланс небольшими партиями и не хотите держать под это отдельного человека, напишите или позвоните, разберём ваш случай.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Калужская обл., Сухиничи, ул. Ленина, 74</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2543556358</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ель пиловочник на пилораму(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>На пилораме приёмка идёт просто: машина встала на весы, приёмщик замерил еловый пиловочник и сразу просит документ на объём. Если рейс не проведён в системе, лес не примут, и водитель стоит у ворот, пока по телефону выясняют, кто будет оформлять.&lt;br&gt; &lt;br&gt;Оформляю ЭСД и QR код на такие рейсы. ЭСД это электронный сопроводительный документ на перевозку древесины, он делается в ФГИС ЛК, государственной системе учёта древесины, и к нему формируется QR код для проверки. Если на приёмке объём не сходится с тем, что числится по складу, поправлю МСД, материально-складской документ, и сведу остатки.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Присылаете породу, объём в кубометрах, откуда и куда идёт машина.&lt;br&gt;2. Присылаете данные перевозчика: марку, госномер, фамилию водителя.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водитель показывает его с телефона или на распечатке.&lt;br&gt; &lt;br&gt;По срокам обычный рейс делаю в течение часа, чаще быстрее. Если машина уже стоит на пилораме и её держат на приёмке, скажите сразу, возьму первой.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий и числится за вашей древесиной. На посту и на весовой он проверяется по QR коду и вопросов не вызывает.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите объём и маршрут, по срокам отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Брянская обл., Дятьково, ул. Ленина, 141</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>2026-07-23T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7246970107</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк вагон(ЭСД и QR на отгрузку)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Лиственницу подали под вагон, замер на нижнем складе один, а весовая на станции показывает другой объём. Разница в кубатуре по обмеру и по весу, пересорт по длинам, часть пачки ушла в другой сортимент. Приёмка упирается в бумагу, вагон стоит, отгрузка встаёт на месте.&lt;br&gt; &lt;br&gt;Мы сводим документ с фактическим объёмом отгрузки и оформляем ЭСД это электронный сопроводительный документ на перевозку древесины, вместе с QR-кодом на рейс. Всё делается во ФГИС ЛК это государственная система учёта древесины. При необходимости поправим МСД это материально-складской документ по вашему складу и подадим ОЛИ это отчёт об использовании лесов, чтобы остатки после погрузки сходились с тем, что реально уехало.&lt;br&gt; &lt;br&gt;Порядок работы:&lt;br&gt;1. Вы пишете породу, сортимент, объём по спецификации и куда идёт вагон или лесовоз.&lt;br&gt;2. Присылаете реквизиты отправителя и получателя, договор или спецификацию, данные по делянке либо складу.&lt;br&gt;3. Мы смотрим, хватает ли остатка в системе под эту отгрузку, и заранее говорим, если чего-то не хватает.&lt;br&gt;4. Получаете готовый ЭСД и QR-код, водитель показывает его на посту, приёмщик сканирует на весовой.&lt;br&gt; &lt;br&gt;По срокам: обычно от получаса до трёх часов в рабочее время, срочные рейсы делаем вне очереди.&lt;br&gt; &lt;br&gt;Документ настоящий, он формируется в государственной системе учёта древесины и числится за вашей организацией, поэтому спокойно проходит проверку на посту и сверку на весовой.&lt;br&gt; &lt;br&gt;Напишите или позвоните, подскажем по вашей отгрузке.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Тайшет, ул. Ленина, 116</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>2026-07-23T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4231722654</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ель пиловочник(ЭСД по фото с телефона)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Пилорама грузит еловый пиловочник, машина уже под воротами, а документа на рейс нет. Водитель нервничает, приёмка на том конце ждёт, и всё встало из-за одной бумаги. В такие моменты обычно и пишут, чаще прямо с телефона из кабины.&lt;br&gt; &lt;br&gt;Оформляем ЭСД, это электронный сопроводительный документ на перевозку древесины. Делаем его в ФГИС ЛК, государственной системе учёта древесины, по вашим данным. Ставить программы, разбираться в личном кабинете и куда-то ехать не нужно, всё решается перепиской и одним звонком.&lt;br&gt; &lt;br&gt;Что прислать и что получите:&lt;br&gt;1. Фото накладной или спецификации, можно снимок экрана. Если бумаги нет, напишите текстом породу, сортимент и объём в кубометрах.&lt;br&gt;2. Точку погрузки и точку выгрузки, кто отправитель и кто получатель груза.&lt;br&gt;3. Госномера тягача и прицепа, фамилию водителя.&lt;br&gt;4. В ответ приходит готовый ЭСД с QR кодом, файлом и картинкой, которую водитель показывает прямо с экрана телефона.&lt;br&gt; &lt;br&gt;По времени обычно от пятнадцати до тридцати минут в рабочее время, срочные рейсы делаем вне очереди, в том числе поздно вечером.&lt;br&gt; &lt;br&gt;Документ настоящий, он проводится через государственную систему и виден в ней по номеру. На посту и на весовой такой ЭСД проверяется как обычно и вопросов не вызывает. Рядом при необходимости закрываем расхождения по объёмам, ведём МСД, это материально-складской документ, и сдаём ОЛИ, отчёт об использовании лесов.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажете что за груз и куда идёт, дальше подскажу что именно с телефона прислать.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Пудож, ул. Ленина, 90</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>2026-08-22T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9513576965</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Хвоя пиловочник(ЭСД под фактический объём)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Знакомая ситуация: по лесной декларации проходит один объём, а на площадку заехал лесовоз совсем с другой цифрой. Пока идёт приёмка и обмер, машина стоит, ЭСД это электронный сопроводительный документ на перевозку древесины, и оформлен он под ту цифру, которая с фактом уже не сходится. Особенно часто так выходит, когда часть хвои сразу уходит в распиловку, а остаток лежит на складе неучтённым.&lt;br&gt; &lt;br&gt;Занимаемся именно такими случаями. Сводим объём в ФГИС ЛК, это государственная система учёта древесины, с тем, что реально лежит и реально едет, после чего оформляем ЭСД уже под фактическую партию. Если разница накопилась за несколько отгрузок, поднимаем историю по поставкам, правим остатки и ведём МСД, это материально-складской документ, чтобы дальше объёмы сходились сами и вопрос не повторялся.&lt;br&gt; &lt;br&gt;Как работаем:&lt;br&gt;1. Присылаете данные по декларации или договору, породу, сортимент и объём партии.&lt;br&gt;2. Говорим, на каком шаге цифры разъехались и что нужно поправить.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом на рейс и сведённые остатки в системе.&lt;br&gt; &lt;br&gt;По срокам: рейс оформляем в пределах получаса, разбор накопленных расхождений занимает от нескольких часов до рабочего дня, зависит от числа отгрузок.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему учёта, документ настоящий и числится за вашими данными, на посту и на весовой он проверяется по QR коду спокойно. При необходимости сдадим и ОЛИ, это отчёт об использовании лесов.&lt;br&gt; &lt;br&gt;Напишите или позвоните, разберём вашу ситуацию и скажем, что делать.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Сафоново, ул. Ленина, 3</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>2026-07-24T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7486730510</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Сосна кругляк вывозка(ЭСД и QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Белый Яр и Верхнекетье живут вывозкой. Машина под сосновым кругляком выходит рано, дорога длинная, и разбираться с документами по пути уже некогда. Чаще всего пишут так: лесовоз загружен, водитель на связи, а рейс в системе не проведён.&lt;br&gt; &lt;br&gt;Делаем ЭСД, это электронный сопроводительный документ на перевозку древесины, и QR код к нему. Оформление идёт в ФГИС ЛК, это государственная система учёта древесины. Отвечаем быстро, потому что понимаем, что на том конце машина, а не переписка.&lt;br&gt; &lt;br&gt;Как это проходит:&lt;br&gt;1. Присылаете рейс: порода, сортимент, объём в кубометрах, точка погрузки и точка выгрузки.&lt;br&gt;2. Присылаете перевозчика: марка и госномер тягача, прицеп, фамилия водителя.&lt;br&gt;3. Сообщаете, на каком основании у вас древесина: договор, декларация или сделка в системе. Если не уверены, что именно у вас есть, пришлите фото бумаг, посмотрим сами.&lt;br&gt;4. Получаете готовый ЭСД с QR кодом файлом, водителю достаточно открыть его в телефоне.&lt;br&gt; &lt;br&gt;По срокам: на сообщение отвечаем в течение нескольких минут, готовый документ по полным данным отдаём за пятнадцать, двадцать минут. Ночной или ранний выезд лучше сказать с вечера, подстроимся.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий и числится за вашей организацией. На посту и на весовой он проверяется сканированием кода и вопросов не вызывает.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите объём и маршрут, посмотрим по вашему рейсу.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Томская обл., Верхнекетский р-н, Белый Яр, ул. Гагарина, 47</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>2026-07-24T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6724986588</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Берёза кругляк на комбинат(ЭСД по договору)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Фанерный кряж берёзы почти всегда едет на комбинат по договору поставки, и приёмка там строгая. Бывает так: машину взвесили, кряж приняли, а водитель вёз только накладную от руки. На следующем рейсе лесовоз тормозят на посту и просят электронный документ, рейс встаёт, комбинат ждёт объём, а по договору идут сроки.&lt;br&gt; &lt;br&gt;Мы оформляем ЭСД это электронный сопроводительный документ на перевозку древесины, и делаем это в ФГИС ЛК это государственная система учёта древесины. Работаем и с разовым рейсом, и с постоянной отгрузкой на комбинат, когда машины идут каждый день по одному договору.&lt;br&gt; &lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Присылаете реквизиты продавца и покупателя, номер и дату договора поставки.&lt;br&gt;2. Присылаете данные рейса: порода берёза, сортимент фанерный кряж, объём, номер тягача и прицепа, водителя, откуда и куда едет.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, который водитель показывает на посту и на весовой, плюс сверку объёма по договору, чтобы отгруженное и принятое сходились.&lt;br&gt; &lt;br&gt;По срокам: если данные готовы, документ делаем в течение пятнадцати минут. На первый рейс по новому договору закладывайте около часа, пока сверяем реквизиты и остатки объёма.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему учёта древесины, документ настоящий и хранится в базе, проверку на посту и на весовой проходит. Ведём и остатки объёма по договору, чтобы к следующему рейсу было понятно, сколько ещё можно везти.&lt;br&gt; &lt;br&gt;Если возите кряж на комбинат и хотите, чтобы бумаги шли ровно с каждым рейсом, напишите или позвоните, посмотрим ваш договор и объёмы.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Костромская обл., Шарья, ул. Ленина, 6</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>2026-08-23T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5150811781</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ель кругляк остатки(документы и учёт ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ситуация из практики: по складу числится один объём еловой древесины, по факту на площадке лежит другой. Что-то ушло рейсами без оформления, что-то перемерили после раскряжёвки, где-то сортимент записали не тот. Пока остаток не сведён, следующая отгрузка встаёт, и проверять расхождение приходится задним числом.&lt;br&gt; &lt;br&gt;Приводим склад в порядок. Ведём МСД, это материально-складской документ по вашей площадке, оформляем ЭСД, это электронный сопроводительный документ на перевозку древесины, готовим ОЛИ, это отчёт об использовании лесов. Всё в ФГИС ЛК, это государственная система учёта древесины.&lt;br&gt; &lt;br&gt;Как разбираем:&lt;br&gt;1. Присылаете выгрузку остатков из системы и свои цифры по складу, хоть в тетради, хоть в таблице.&lt;br&gt;2. Присылаете, что уходило за период: рейсы, объёмы, покупатели, чем оформляли.&lt;br&gt;3. Показываем, где именно разошлось и на сколько кубометров, и говорим, чем это закрывается.&lt;br&gt;4. Проводим недостающие документы и приводим остаток к фактическому.&lt;br&gt; &lt;br&gt;По срокам: первичный разбор по вашим данным делаем в течение дня, дальше зависит от того, сколько накопилось за период. Небольшой склад закрываем за пару дней.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документы настоящие и числятся за вашей организацией. Никаких схем и подчисток, только то, что можно показать при проверке.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите объём склада и за какой период разошлось.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Республика Коми, Инта, ул. Горького, 12</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>2026-07-25T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>6151148826</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Осина дрова(QR код на короткий рейс)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Осина на дрова и низкосортный кругляк почти всегда едут мелкими рейсами. Сегодня две машины на котельную, завтра пара коротышей на пилораму в соседний район, потом кому-то бортовой на подтопку. Объём смешной, а документ на каждую машину нужен ровно такой же, как на полный лесовоз, и водитель встаёт на выезде, потому что показать нечего.&lt;br&gt; &lt;br&gt;Оформляем на такие перевозки ЭСД, это электронный сопроводительный документ на перевозку древесины, с QR кодом на каждую машину. Всё делается в ФГИС ЛК, это государственная система учёта древесины. Заодно следим, чтобы дрова и низкосорт списывались с вашего остатка правильно и объём к концу месяца сходился. Если нужно, ведём МСД, это материально-складской документ по складу, и ОЛИ, это отчёт об использовании лесов.&lt;br&gt; &lt;br&gt;Порядок простой:&lt;br&gt;1. Присылаете отправителя и получателя, породу, сортимент и объём по машине.&lt;br&gt;2. Добавляете номер автомобиля, фамилию водителя и маршрут.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом, водитель показывает его с телефона или везёт распечатку.&lt;br&gt; &lt;br&gt;Первый рейс собираем примерно за полчаса после ваших данных, дальше каждая следующая машина занимает несколько минут, так что десяток коротких ходок за смену закрываем спокойно, в том числе вечером и в выходные.&lt;br&gt; &lt;br&gt;Документ настоящий, проводится через государственную систему, у него свой номер и статус. На посту и на весовой такой QR код читается и проверку проходит.&lt;br&gt; &lt;br&gt;Напишите или позвоните, скажите породу, объём и куда возите, посмотрим ваш случай и оформим первый рейс.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Нижегородская обл., Шахунья, ул. Советская, 12</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>2026-08-24T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>2026-07-25T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -16039,7 +18441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -16196,7 +18598,11 @@
           <t>AvitoDateEnd</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="n"/>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -17221,6 +19627,366 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>2026-08-06T06:42:07+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3146294132</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_21_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_21_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_21_3.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк лесовоз(ЭСД и QR к сделке)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Продали лиственницу с делянки, покупатель просит документы, а машина уже стоит под погрузкой. У продавца объём не поставлен на учёт, у покупателя нет ЭСД (электронный сопроводительный документ на перевозку древесины) на рейс. Сделка встала, водитель ждёт.&lt;br&gt; &lt;br&gt;Веду сделку купли-продажи древесины по документам от начала до конца. ФГИС ЛК это государственная система учёта древесины. Ставлю объём на учёт, оформляю МСД (материально-складской документ), провожу саму сделку между сторонами в системе, готовлю ЭСД с QR кодом на каждый рейс. Если нужно, сдаю ОЛИ (отчёт об использовании лесов) и лесную декларацию.&lt;br&gt; &lt;br&gt;Порядок работы:&lt;br&gt;1. Вы присылаете ИНН обеих сторон, породу, сортимент и объём.&lt;br&gt;2. Уточняем маршрут, перевозчика и номер машины.&lt;br&gt;3. Я провожу сделку в системе и оформляю складские документы.&lt;br&gt;4. Вы получаете ЭСД с QR кодом на телефон или на печать, машина выезжает.&lt;br&gt; &lt;br&gt;По срокам: при готовых данных ЭСД выходит в течение часа, постановка объёмов и проведение сделки обычно в тот же день.&lt;br&gt; &lt;br&gt;Всё идёт через государственную систему, от вашего личного кабинета или по доверенности. Документ настоящий, отражается в базе, на посту и на весовой сканируется по QR коду и проверку проходит.&lt;br&gt; &lt;br&gt;Работаю по Иркутской области и по другим регионам, лиственница, сосна, ель, берёза. Напишите или позвоните, разберём вашу ситуацию и скажу, какие данные понадобятся.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Иркутск, ул. Ленина, 6</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-08-22T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1231336395</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_3.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>300</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Сосна кругляк под отгрузку(QR код на партию)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Покупатель ждёт машину, лес на площадке лежит, а по документам партия ещё не собрана. Пока объём не проведён и на рейс нет QR кода, водителя на весовой развернут, и отгрузка встанет на день, а то и на два. История обычная, особенно когда партия набирается с нескольких делянок.&lt;br&gt; &lt;br&gt;Помогаю собрать партию сосны под конкретную отгрузку и провести её через ФГИС ЛК, это государственная система учёта древесины. Свожу объёмы по сортиментам, ставлю партию на учёт, оформляю МСД, это материально-складской документ, и выпускаю ЭСД, это электронный сопроводительный документ на перевозку древесины, с QR кодом на каждый рейс. При необходимости дальше веду ОЛИ, это отчёт об использовании лесов.&lt;br&gt; &lt;br&gt;Порядок работы:&lt;br&gt;1. Присылаете данные по партии: порода, сортимент, объём, откуда лес и куда идёт машина.&lt;br&gt;2. Присылаете реквизиты покупателя и перевозчика, номер тягача и прицепа, данные водителя.&lt;br&gt;3. Получаете готовый ЭСД с QR кодом и сведённый остаток по складу, водитель показывает код с телефона или везёт распечатку.&lt;br&gt; &lt;br&gt;По срокам: при полных данных документ на рейс делаю в течение часа, обычно быстрее. Сбор партии и сведение объёмов занимает от нескольких часов до рабочего дня, зависит от того, в каком виде у вас сейчас учёт.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему от вашего юрлица. Документ настоящий, на посту и на весовой проверку проходит, инспектор видит его в базе по QR коду.&lt;br&gt; &lt;br&gt;Если не понимаете, что именно нужно оформить на вашу партию, напишите или позвоните. Разберём вашу ситуацию и скажу, с чего начинать.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Красноярский край, Красноярск, пр-т Мира, 10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-08-23T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>9619198952</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>79852671075</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>350</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Сосна кругляк деловой(документы ФГИС ЛК с нуля)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Бригада три человека, вальщик, тракторист и водитель. Лес валят нормально, а с учётом никто раньше не работал: делянка есть, лесовоз есть, а в государственной базе по бригаде пусто. Первый же рейс упирается в то, что предъявить на посту нечего.&lt;br&gt; &lt;br&gt;Ставим учёт с нуля. Заводим и приводим в порядок ваш профиль в ФГИС ЛК, это государственная система учёта древесины. Оформляем МСД, материально-складской документ по складу и делянке, ставим объёмы на баланс по породам и сортиментам, готовим ЭСД, электронный сопроводительный документ на перевозку древесины, с QR кодом на каждый рейс. Дальше ведём ОЛИ, отчёт об использовании лесов, и лесную декларацию, чтобы отчётность не копилась.&lt;br&gt; &lt;br&gt;Как начинаем:&lt;br&gt;1. Присылаете договор или документ на лесной участок, реквизиты и данные подписи руководителя.&lt;br&gt;2. Скидываете, что уже заготовлено: породы, сортименты, кубатура, площадка хранения.&lt;br&gt;3. По каждому рейсу даёте машину, водителя, объём и получателя.&lt;br&gt;4. Получаете готовый ЭСД с QR кодом на телефон водителя и порядок в базе.&lt;br&gt; &lt;br&gt;Первичная постановка учёта занимает один рабочий день, документ на рейс готовим в течение часа.&lt;br&gt; &lt;br&gt;Всё проводится через государственную систему, документ настоящий, на посту и на весовой проходит проверку. Работаем в штатном порядке, как он прописан в законе.&lt;br&gt; &lt;br&gt;Работаем с небольшими бригадами, объём в кубах значения не имеет. Напишите или позвоните, разберём вашу ситуацию по шагам.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Великий Новгород, ул. Большая Санкт-Петербургская, 39</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-08-24T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-07-25T18:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -2244,6 +2244,11 @@
           <t>Садовые растения</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Хвойные растения</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>ФГИС ЛК объемы</t>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Q8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -17142,7 +17142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AD45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79852671075</t>
+          <t>79824510018</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -2326,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="B1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="B1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6923,7 +6923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="B1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7500,7 +7500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ72"/>
+  <dimension ref="A1:AJ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -17050,6 +17050,2426 @@
       <c r="AJ72" t="inlineStr">
         <is>
           <t>2026-07-25T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3777371400</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Сосна кругляк лесовоз(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД и QR код на вывоз леса через ФГИС ЛК.
+Машина под погрузкой, покупатель ждёт, а сопроводительного документа на рейс нет. Это закрывается быстро, если декларация и остатки в системе в порядке: 15 минут с момента, когда пришли данные по рейсу.
+Работаем с хвойным кругляком 6 метров, диаметр от 20 см, и с другими сортиментами.
+Что берём на себя:
+- ЭСД и QR код водителю на каждую машину
+- проверку остатков перед отгрузкой, чтобы документ не завернули
+- если фактический объём разошёлся с заявленным, помогаем законно уточнить декларацию
+Оформляем доверенность в системе, логин и пароль от вашего кабинета не нужны.
+Напишите, что у вас по рейсу, скажу срок и что потребуется от вас.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_3.png</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Сегежа, ул. Ленина, 9</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>2026-08-28T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>2026-07-29T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3381851450</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ель пиловочник хвоя(QR код на рейс)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Делаем QR коды и ЭСД на перевозку леса через ФГИС ЛК.
+Ситуация знакомая: лес готов, машина есть, а документа на рейс нет. При нормальных остатках и действующей декларации выпускаем за 15 минут после ваших данных по перевозке.
+Ель и сосна, пиловочник 6 метров, диаметр от 20 см.
+В работе:
+- ЭСД на рейс и QR код для водителя
+- сверка объёмов до отгрузки, а не после
+- если оформлено с ошибкой, аннулируем и выпускаем документ заново по правилам
+Доверенность в системе оформляется один раз, пароли от кабинета не запрашиваю.
+Напишите объём и маршрут, отвечу по срокам сегодня же.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_3.png</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Кемь, Пролетарский пр-т, 24</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>2026-08-28T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>2026-07-29T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2553302255</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Берёза кругляк баланс(ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на вывоз баланса и кругляка через ФГИС ЛК.
+Балансовая берёза едет объёмами, и на каждый рейс нужен свой документ. Держим это на потоке, чтобы машины не ждали бумаг.
+Берёза и осина, длина 6 метров, диаметр от 20 см.
+Что делаем:
+- электронный сопроводительный документ на каждый рейс
+- проверку данных перед выпуском, чтобы не было отказа
+- если объём по факту отличается от заявленного, помогаем законно уточнить декларацию
+Срок по рутинному ЭСД: около 15 минут после ваших данных по машине. Если данные расходятся, сначала разбираемся с декларацией, срок скажу отдельно.
+Напишите ситуацию, даже если просто нужен ЭСД без всяких расхождений, скажу срок.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_3.png</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Республика Коми, Емва, ул. Первомайская, 14</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>2026-08-28T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>2026-07-29T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4613998496</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк(QR код и ЭСД на вывоз)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на вывоз лиственницы и хвойного кругляка.
+Основной запрос, с которым приходят: нужен документ на рейс прямо сейчас. Если декларация действует и остатки сходятся, выпускаем за 15 минут после ваших данных.
+Лиственница и сосна, 6 метров, диаметр от 20 см.
+Берём на себя:
+- ЭСД и QR код на каждую машину
+- проверку остатков и данных перед отгрузкой
+- законное уточнение декларации, если фактический объём разошёлся с заявленным
+Работаем по доверенности в системе, доступ к вашему паролю не нужен.
+Опишите задачу, скажу что делать и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Зима, ул. Ленина, 5</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>2026-08-28T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2000316878</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник деловой(QR код на лес)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на партию леса, оформляем удалённо через ФГИС ЛК.
+Если водителю нечем подтвердить перевозку, документ нужен до выезда, а не после. Выпускаем за 15 минут с момента, когда есть данные по рейсу и порядок в остатках.
+Сосна деловая, пиловочник 6 метров, диаметр от 20 см.
+Что входит:
+- ЭСД и QR код для водителя
+- проверка остатков и данных до отгрузки
+- помощь с законным уточнением декларации, если объёмы разошлись
+Доверенность в системе, пароли от кабинета не передаются.
+Напишите свою ситуацию, скажу срок и что нужно от вас.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Иркутская обл., пгт Чунский, ул. Комарова, 11</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>2026-08-29T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>2026-07-30T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3255397507</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Кедр кругляк отгрузка(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код под отгрузку леса, оформляем через ФГИС ЛК.
+Отгрузка стоит ровно до тех пор, пока нет документа на рейс. Убираем эту паузу: при порядке в декларации и остатках ЭСД выходит за 15 минут после ваших данных.
+Кедр, сосна, лиственница, кругляк 6 метров, диаметр от 20 см.
+Что делаем:
+- документ на рейс и QR код водителю
+- проверку данных перед выпуском
+- законное уточнение декларации, если фактический объём другой
+Разбор расхождений занимает больше времени, обычно рабочий день, об этом говорю сразу.
+Оформляем доверенность в системе, логин и пароль не нужны.
+Опишите задачу, отвечу что можно сделать и за какой срок.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Киренск, ул. Красноармейская, 8</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Кедр</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>2026-08-29T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6814079693</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ель кругляк на комбинат(ЭСД по договору)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на поставки леса на комбинат и другим покупателям.
+Если отгрузка встала из-за документа на рейс, закрываем это за 15 минут при нормальных остатках. Дальше можно вести так каждую поставку, чтобы вопрос не возвращался.
+Ель и берёза, кругляк 6 метров, диаметр от 20 см.
+В работе:
+- ЭСД на каждый рейс и QR код водителю
+- контроль остатков в системе перед отгрузкой
+- законное уточнение декларации при расхождении объёмов
+Работаем по доверенности, пароли от кабинета не запрашиваю.
+Напишите объёмы и периодичность поставок, посчитаю и скажу срок.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Сокол, ул. Советская, 30</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>2026-08-29T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>2026-07-30T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>8877817376</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Сосна кругляк вывозка(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на вывозку леса через ФГИС ЛК.
+Чаще всего нужен один документ и срочно: машина готова, а рейс без бумаг не выпустить. При действующей декларации это 15 минут после ваших данных.
+Сосна и ель, кругляк 6 метров, диаметр от 20 см.
+Что берём:
+- ЭСД и QR код на каждую машину
+- проверку остатков до отгрузки
+- законное уточнение декларации, если объём по факту не тот
+Доверенность в системе оформляется один раз, пароль от кабинета остаётся у вас.
+Напишите, что не так с документами, отвечу в течение часа.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Вытегра, пр-т Ленина, 42</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>2026-08-29T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6805772604</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Осина дрова баланс(QR код на рейс)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на дрова и низкосортный кругляк.
+Объём небольшой, а документ на рейс нужен такой же, как на деловой лес. Оформляем без лишней переписки: 15 минут после ваших данных, если с остатками порядок.
+Осина и берёза, длина 6 метров, диаметр от 20 см.
+Делаем:
+- ЭСД и QR код водителю
+- проверку данных перед выпуском документа
+- законное уточнение декларации при расхождении объёмов
+Работаем по доверенности в системе, пароли не нужны.
+Напишите, что нужно оформить, скажу срок сегодня же.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Харовск, ул. Октябрьская, 7</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>2026-08-30T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>2026-07-31T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7863002342</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Пихта кругляк хвоя(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на хвойный кругляк через ФГИС ЛК.
+Когда рейсов много, документы начинают отставать от отгрузок. Наводим порядок и дальше ведём на потоке, чтобы машины не простаивали из-за бумаг.
+Пихта, ель, сосна, кругляк 6 метров, диаметр от 20 см.
+Что входит:
+- ЭСД и QR код на каждый рейс
+- проверка остатков перед отгрузкой
+- законное уточнение декларации, если фактический объём разошёлся
+Рутинный документ выходит за 15 минут после ваших данных. Разбор расхождений считаем отдельно, сроки скажу честно.
+Доверенность в системе, доступ к паролю не требуется.
+Напишите ситуацию, скажу срок и порядок работы.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Кировская обл., Луза, ул. Ленина, 23</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Пихта</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>2026-08-30T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5503135489</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Берёза пиловочник(ЭСД на каждую машину)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ЭСД на каждую машину при вывозе леса.
+Подходит и на одну отгрузку, и на постоянный поток. Разово тоже берём, никакого минимального объёма нет.
+Берёза и осина, пиловочник 6 метров, диаметр от 20 см.
+Что делаем:
+- документ на рейс и QR код водителю
+- проверку остатков и данных до выпуска
+- законное уточнение декларации при расхождении объёмов
+Срок по рутинному ЭСД около 15 минут с момента ваших данных по машине.
+Работаем по доверенности в системе, логин и пароль не передаются.
+Напишите количество рейсов, посчитаю и скажу срок.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Кировская обл., Белая Холуница, ул. Ленина, 5</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>2026-08-30T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9188991995</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник распил(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на пиловочник под распил.
+Лес заготовлен, покупатель есть, а отгрузка стоит из-за документа на рейс. Это решается за 15 минут, если декларация действует и остатки сходятся.
+Сосна и ель, пиловочник 6 метров, диаметр от 20 см.
+Берём на себя:
+- ЭСД и QR код водителю на каждую машину
+- проверку данных перед выпуском
+- законное уточнение декларации, если объём по факту отличается
+Доверенность в системе, пароли от кабинета остаются у вас.
+Опишите ситуацию, скажу что делать и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Боровичи, ул. Международная, 12</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>2026-07-31T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7978379002</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR код на вывозку)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>QR коды и ЭСД на вывозку хвойного леса.
+Работаем и с разовой машиной, и с потоком отгрузок. Документ на рейс выходит за 15 минут после ваших данных, когда с остатками порядок.
+Сосна и ель, кругляк 6 метров, диаметр от 20 см.
+В работе:
+- ЭСД и QR код на каждую машину
+- сверка фактических объёмов с данными системы до отгрузки
+- законное уточнение декларации при расхождении
+Оформляем доверенность в системе, пароль от кабинета не нужен.
+Напишите объёмы, отвечу по срокам и порядку работы.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Пестово, ул. Советская, 10</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>2026-08-01T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7028010874</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ель пиловочник брус(ЭСД под объём)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ЭСД под фактический объём отгрузки.
+Бывает, что в документах один объём, а по факту грузится другой. Помогаем привести данные в соответствие законным путём, через уточнение декларации, и дальше вести учёт корректно.
+Ель и сосна, пиловочник 6 метров, диаметр от 20 см.
+Что делаем:
+- ЭСД на рейс и QR код водителю
+- сверку фактического объёма с данными в системе
+- уточнение декларации, когда цифры разошлись
+Рутинный документ занимает около 15 минут. Работа с расхождениями дольше, обычно рабочий день.
+Доверенность в системе, логин и пароль не запрашиваю.
+Напишите, какие объёмы и что не сходится, скажу порядок действий.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Окуловка, ул. Кирова, 6</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>2026-08-01T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7116069769</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Сосна кругляк деловой(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на деловой кругляк, оформляем через ФГИС ЛК.
+Машина под погрузкой, а документа на рейс нет. Закрываем это быстро, вам остаётся заготовка и отгрузка.
+Сосна и лиственница, кругляк 6 метров, диаметр от 20 см.
+Что берём на себя:
+- ЭСД и QR код водителю на каждый рейс
+- контроль остатков перед отгрузкой
+- законное уточнение декларации, если объём по факту другой
+Срок по рутинному документу около 15 минут после ваших данных по машине.
+Работаем по доверенности в системе, пароли не передаются.
+Опишите задачу, скажу что и в какой срок.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_3.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Подпорожье, ул. Свирская, 14</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>2026-08-31T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>2026-08-01T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2089892052</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Лиственница пиловочник(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на лиственницу и другой пиловочник.
+Если объёмы не проходят или рейс не выпустить без документа, помогаем разобраться и оформить всё по правилам.
+Лиственница, сосна, ель, пиловочник 6 метров, диаметр от 20 см.
+Делаем:
+- ЭСД и QR код на каждую машину
+- сверку объёмов до отгрузки
+- законное уточнение декларации при расхождении данных
+Рутинный ЭСД выходит за 15 минут с момента ваших данных. Разбор расхождений дольше, скажу срок сразу.
+Доверенность в системе, доступ к паролю не нужен.
+Напишите свою ситуацию, отвечу что можно сделать и за какой срок.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Лодейное Поле, пр-т Ленина, 28</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>2026-08-01T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>5010799934</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Сосна кругляк под погрузку(QR и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на рейс, оформляем через ФГИС ЛК.
+Машина под погрузкой, покупатель ждёт, а сопроводительного документа нет. При действующей декларации и нормальных остатках это 15 минут после ваших данных по рейсу.
+Сосна и ель, кругляк 6 метров, диаметр от 20 см.
+Что делаем:
+- ЭСД и QR код водителю на каждую машину
+- проверку остатков и данных декларации перед отгрузкой
+- законное уточнение декларации, если фактический объём отличается
+Если данные расходятся, сначала разбираемся с декларацией, срок обсуждаем отдельно.
+Работаем по доверенности в системе, пароли от вашего кабинета передавать не нужно.
+Напишите свою ситуацию, отвечу что можно сделать и за какой срок.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_3.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Волхов, ул. Волгоградская, 9</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>2026-08-27T13:15:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>2026-07-28T13:15:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9264196768</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ель пиловочник рейс(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>QR код и ЭСД на каждый рейс, ведём ФГИС ЛК за вас.
+Декларация оформлена, лес заготовлен, а с документами на каждую машину постоянная запара. Берём это на себя целиком.
+Ель и сосна, пиловочник 6 метров, диаметр от 20 см.
+В работе:
+- ЭСД и QR код водителю
+- сверка фактических объёмов с данными в системе
+- законное уточнение декларации, если данные разошлись
+Сроки честные: рутинный ЭСД около 15 минут с момента, когда пришли данные по машине. Разбор расхождений занимает больше, обычно рабочий день.
+Оформляем доверенность в системе, логин и пароль от кабинета не запрашиваю.
+Опишите, что у вас происходит, скажу с чего начать.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_3.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Валдай, ул. Победы, 12</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>2026-08-27T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -17142,7 +19562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD45"/>
+  <dimension ref="B1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20066,7 +22486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="B1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -17077,13 +17077,13 @@
       <c r="F73" t="inlineStr">
         <is>
           <t>Оформляем ЭСД и QR код на вывоз леса через ФГИС ЛК.
-Машина под погрузкой, покупатель ждёт, а сопроводительного документа на рейс нет. Это закрывается быстро, если декларация и остатки в системе в порядке: 15 минут с момента, когда пришли данные по рейсу.
+Машина под погрузкой, покупатель ждёт, а сопроводительного документа на рейс нет. Это закрывается быстро: обычно 15 минут с момента, когда пришли данные по рейсу.
 Работаем с хвойным кругляком 6 метров, диаметр от 20 см, и с другими сортиментами.
 Что берём на себя:
 - ЭСД и QR код водителю на каждую машину
-- проверку остатков перед отгрузкой, чтобы документ не завернули
-- если фактический объём разошёлся с заявленным, помогаем законно уточнить декларацию
-Оформляем доверенность в системе, логин и пароль от вашего кабинета не нужны.
+- проверку данных перед отгрузкой, чтобы документ не завернули
+- работаем и когда своих остатков в системе нет
+Оформление полностью на нашей стороне. Своя декларация, кабинет и ЭЦП вам не нужны.
 Напишите, что у вас по рейсу, скажу срок и что потребуется от вас.</t>
         </is>
       </c>
@@ -17211,13 +17211,13 @@
       <c r="F74" t="inlineStr">
         <is>
           <t>Делаем QR коды и ЭСД на перевозку леса через ФГИС ЛК.
-Ситуация знакомая: лес готов, машина есть, а документа на рейс нет. При нормальных остатках и действующей декларации выпускаем за 15 минут после ваших данных по перевозке.
+Ситуация знакомая: лес готов, машина есть, а документа на рейс нет. Выпускаем обычно за 15 минут после ваших данных по перевозке.
 Ель и сосна, пиловочник 6 метров, диаметр от 20 см.
 В работе:
 - ЭСД на рейс и QR код для водителя
-- сверка объёмов до отгрузки, а не после
+- сверка объёма и породы до отгрузки, а не после
 - если оформлено с ошибкой, аннулируем и выпускаем документ заново по правилам
-Доверенность в системе оформляется один раз, пароли от кабинета не запрашиваю.
+Всё оформление берём на себя. От вас данные по машине, свой кабинет в системе не понадобится.
 Напишите объём и маршрут, отвечу по срокам сегодня же.</t>
         </is>
       </c>
@@ -17350,8 +17350,8 @@
 Что делаем:
 - электронный сопроводительный документ на каждый рейс
 - проверку данных перед выпуском, чтобы не было отказа
-- если объём по факту отличается от заявленного, помогаем законно уточнить декларацию
-Срок по рутинному ЭСД: около 15 минут после ваших данных по машине. Если данные расходятся, сначала разбираемся с декларацией, срок скажу отдельно.
+- оформляем, даже если своей декларации у вас нет
+Срок по обычному рейсу: около 15 минут после ваших данных по машине. Если случай нестандартный, скажу срок сразу и честно.
 Напишите ситуацию, даже если просто нужен ЭСД без всяких расхождений, скажу срок.</t>
         </is>
       </c>
@@ -17479,13 +17479,13 @@
       <c r="F76" t="inlineStr">
         <is>
           <t>QR код и ЭСД на вывоз лиственницы и хвойного кругляка.
-Основной запрос, с которым приходят: нужен документ на рейс прямо сейчас. Если декларация действует и остатки сходятся, выпускаем за 15 минут после ваших данных.
+Основной запрос, с которым приходят: нужен документ на рейс прямо сейчас. Обычно выпускаем за 15 минут после ваших данных.
 Лиственница и сосна, 6 метров, диаметр от 20 см.
 Берём на себя:
 - ЭСД и QR код на каждую машину
-- проверку остатков и данных перед отгрузкой
-- законное уточнение декларации, если фактический объём разошёлся с заявленным
-Работаем по доверенности в системе, доступ к вашему паролю не нужен.
+- проверку данных по рейсу перед отгрузкой
+- берём объём на себя, когда свои остатки не подходят
+Своя декларация и доступ в систему вам не нужны, документ приходит готовым.
 Опишите задачу, скажу что делать и в какой срок.</t>
         </is>
       </c>
@@ -17613,13 +17613,13 @@
       <c r="F77" t="inlineStr">
         <is>
           <t>QR код и ЭСД на партию леса, оформляем удалённо через ФГИС ЛК.
-Если водителю нечем подтвердить перевозку, документ нужен до выезда, а не после. Выпускаем за 15 минут с момента, когда есть данные по рейсу и порядок в остатках.
+Если водителю нечем подтвердить перевозку, документ нужен до выезда, а не после. Выпускаем за 15 минут с момента, когда есть данные по рейсу.
 Сосна деловая, пиловочник 6 метров, диаметр от 20 см.
 Что входит:
 - ЭСД и QR код для водителя
-- проверка остатков и данных до отгрузки
-- помощь с законным уточнением декларации, если объёмы разошлись
-Доверенность в системе, пароли от кабинета не передаются.
+- проверка данных по машине до отгрузки
+- работаем и когда своих документов на объём нет
+Оформляем со своей стороны. Вам не нужны ни кабинет, ни электронная подпись.
 Напишите свою ситуацию, скажу срок и что нужно от вас.</t>
         </is>
       </c>
@@ -17747,14 +17747,14 @@
       <c r="F78" t="inlineStr">
         <is>
           <t>ЭСД и QR код под отгрузку леса, оформляем через ФГИС ЛК.
-Отгрузка стоит ровно до тех пор, пока нет документа на рейс. Убираем эту паузу: при порядке в декларации и остатках ЭСД выходит за 15 минут после ваших данных.
+Отгрузка стоит ровно до тех пор, пока нет документа на рейс. Убираем эту паузу: обычно ЭСД выходит за 15 минут после ваших данных.
 Кедр, сосна, лиственница, кругляк 6 метров, диаметр от 20 см.
 Что делаем:
 - документ на рейс и QR код водителю
 - проверку данных перед выпуском
-- законное уточнение декларации, если фактический объём другой
-Разбор расхождений занимает больше времени, обычно рабочий день, об этом говорю сразу.
-Оформляем доверенность в системе, логин и пароль не нужны.
+- закрываем рейс, если по своим документам не проходит
+Нестандартные случаи занимают больше времени, об этом говорю сразу, до начала работы.
+Работаем так, что от вас нужны только данные по рейсу. Своя декларация не требуется.
 Опишите задачу, отвечу что можно сделать и за какой срок.</t>
         </is>
       </c>
@@ -17882,13 +17882,13 @@
       <c r="F79" t="inlineStr">
         <is>
           <t>Оформляем ЭСД на поставки леса на комбинат и другим покупателям.
-Если отгрузка встала из-за документа на рейс, закрываем это за 15 минут при нормальных остатках. Дальше можно вести так каждую поставку, чтобы вопрос не возвращался.
+Если отгрузка встала из-за документа на рейс, закрываем это обычно за 15 минут. Дальше можно вести так каждую поставку, чтобы вопрос не возвращался.
 Ель и берёза, кругляк 6 метров, диаметр от 20 см.
 В работе:
 - ЭСД на каждый рейс и QR код водителю
-- контроль остатков в системе перед отгрузкой
-- законное уточнение декларации при расхождении объёмов
-Работаем по доверенности, пароли от кабинета не запрашиваю.
+- контроль данных перед каждой отгрузкой
+- работаем и без ваших остатков в системе
+Оформление на нас. Свой кабинет, подпись и декларацию заводить не придётся.
 Напишите объёмы и периодичность поставок, посчитаю и скажу срок.</t>
         </is>
       </c>
@@ -18016,13 +18016,13 @@
       <c r="F80" t="inlineStr">
         <is>
           <t>QR код и ЭСД на вывозку леса через ФГИС ЛК.
-Чаще всего нужен один документ и срочно: машина готова, а рейс без бумаг не выпустить. При действующей декларации это 15 минут после ваших данных.
+Чаще всего нужен один документ и срочно: машина готова, а рейс без бумаг не выпустить. Обычно это 15 минут после ваших данных.
 Сосна и ель, кругляк 6 метров, диаметр от 20 см.
 Что берём:
 - ЭСД и QR код на каждую машину
-- проверку остатков до отгрузки
-- законное уточнение декларации, если объём по факту не тот
-Доверенность в системе оформляется один раз, пароль от кабинета остаётся у вас.
+- проверку данных до отгрузки
+- оформляем под ваш объём, свои документы для этого не нужны
+Оформление полностью на нашей стороне. Своя декларация, кабинет и ЭЦП вам не нужны.
 Напишите, что не так с документами, отвечу в течение часа.</t>
         </is>
       </c>
@@ -18150,13 +18150,13 @@
       <c r="F81" t="inlineStr">
         <is>
           <t>QR код и ЭСД на дрова и низкосортный кругляк.
-Объём небольшой, а документ на рейс нужен такой же, как на деловой лес. Оформляем без лишней переписки: 15 минут после ваших данных, если с остатками порядок.
+Объём небольшой, а документ на рейс нужен такой же, как на деловой лес. Оформляем без лишней переписки: обычно 15 минут после ваших данных.
 Осина и берёза, длина 6 метров, диаметр от 20 см.
 Делаем:
 - ЭСД и QR код водителю
 - проверку данных перед выпуском документа
-- законное уточнение декларации при расхождении объёмов
-Работаем по доверенности в системе, пароли не нужны.
+- работаем и когда своих остатков в системе нет
+Всё оформление берём на себя. От вас данные по машине, свой кабинет в системе не понадобится.
 Напишите, что нужно оформить, скажу срок сегодня же.</t>
         </is>
       </c>
@@ -18288,10 +18288,10 @@
 Пихта, ель, сосна, кругляк 6 метров, диаметр от 20 см.
 Что входит:
 - ЭСД и QR код на каждый рейс
-- проверка остатков перед отгрузкой
-- законное уточнение декларации, если фактический объём разошёлся
+- проверка данных перед отгрузкой
+- оформляем, даже если своей декларации у вас нет
 Рутинный документ выходит за 15 минут после ваших данных. Разбор расхождений считаем отдельно, сроки скажу честно.
-Доверенность в системе, доступ к паролю не требуется.
+Своя декларация и доступ в систему вам не нужны, документ приходит готовым.
 Напишите ситуацию, скажу срок и порядок работы.</t>
         </is>
       </c>
@@ -18423,10 +18423,10 @@
 Берёза и осина, пиловочник 6 метров, диаметр от 20 см.
 Что делаем:
 - документ на рейс и QR код водителю
-- проверку остатков и данных до выпуска
-- законное уточнение декларации при расхождении объёмов
+- проверку данных по рейсу до выпуска
+- берём объём на себя, когда свои остатки не подходят
 Срок по рутинному ЭСД около 15 минут с момента ваших данных по машине.
-Работаем по доверенности в системе, логин и пароль не передаются.
+Оформляем со своей стороны. Вам не нужны ни кабинет, ни электронная подпись.
 Напишите количество рейсов, посчитаю и скажу срок.</t>
         </is>
       </c>
@@ -18554,13 +18554,13 @@
       <c r="F84" t="inlineStr">
         <is>
           <t>QR код и ЭСД на пиловочник под распил.
-Лес заготовлен, покупатель есть, а отгрузка стоит из-за документа на рейс. Это решается за 15 минут, если декларация действует и остатки сходятся.
+Лес заготовлен, покупатель есть, а отгрузка стоит из-за документа на рейс. Обычно это решается за 15 минут.
 Сосна и ель, пиловочник 6 метров, диаметр от 20 см.
 Берём на себя:
 - ЭСД и QR код водителю на каждую машину
 - проверку данных перед выпуском
-- законное уточнение декларации, если объём по факту отличается
-Доверенность в системе, пароли от кабинета остаются у вас.
+- закрываем рейс, если по своим документам не проходит
+Работаем так, что от вас нужны только данные по рейсу. Своя декларация не требуется.
 Опишите ситуацию, скажу что делать и в какой срок.</t>
         </is>
       </c>
@@ -18688,13 +18688,13 @@
       <c r="F85" t="inlineStr">
         <is>
           <t>QR коды и ЭСД на вывозку хвойного леса.
-Работаем и с разовой машиной, и с потоком отгрузок. Документ на рейс выходит за 15 минут после ваших данных, когда с остатками порядок.
+Работаем и с разовой машиной, и с потоком отгрузок. Документ на рейс выходит обычно за 15 минут после ваших данных.
 Сосна и ель, кругляк 6 метров, диаметр от 20 см.
 В работе:
 - ЭСД и QR код на каждую машину
-- сверка фактических объёмов с данными системы до отгрузки
-- законное уточнение декларации при расхождении
-Оформляем доверенность в системе, пароль от кабинета не нужен.
+- сверка объёма по факту загрузки
+- работаем и без ваших остатков в системе
+Оформление на нас. Свой кабинет, подпись и декларацию заводить не придётся.
 Напишите объёмы, отвечу по срокам и порядку работы.</t>
         </is>
       </c>
@@ -18822,14 +18822,14 @@
       <c r="F86" t="inlineStr">
         <is>
           <t>ЭСД под фактический объём отгрузки.
-Бывает, что в документах один объём, а по факту грузится другой. Помогаем привести данные в соответствие законным путём, через уточнение декларации, и дальше вести учёт корректно.
+Бывает, что своих документов на нужный объём просто нет. Оформляем так, чтобы отгрузка прошла корректно, а учёт дальше вёлся в порядке.
 Ель и сосна, пиловочник 6 метров, диаметр от 20 см.
 Что делаем:
 - ЭСД на рейс и QR код водителю
-- сверку фактического объёма с данными в системе
-- уточнение декларации, когда цифры разошлись
+- сверку объёма по факту загрузки
+- оформляем под ваш объём, свои документы для этого не нужны
 Рутинный документ занимает около 15 минут. Работа с расхождениями дольше, обычно рабочий день.
-Доверенность в системе, логин и пароль не запрашиваю.
+Оформление полностью на нашей стороне. Своя декларация, кабинет и ЭЦП вам не нужны.
 Напишите, какие объёмы и что не сходится, скажу порядок действий.</t>
         </is>
       </c>
@@ -18961,10 +18961,10 @@
 Сосна и лиственница, кругляк 6 метров, диаметр от 20 см.
 Что берём на себя:
 - ЭСД и QR код водителю на каждый рейс
-- контроль остатков перед отгрузкой
-- законное уточнение декларации, если объём по факту другой
+- контроль данных перед отгрузкой
+- работаем и когда своих остатков в системе нет
 Срок по рутинному документу около 15 минут после ваших данных по машине.
-Работаем по доверенности в системе, пароли не передаются.
+Всё оформление берём на себя. От вас данные по машине, свой кабинет в системе не понадобится.
 Опишите задачу, скажу что и в какой срок.</t>
         </is>
       </c>
@@ -19096,10 +19096,10 @@
 Лиственница, сосна, ель, пиловочник 6 метров, диаметр от 20 см.
 Делаем:
 - ЭСД и QR код на каждую машину
-- сверку объёмов до отгрузки
-- законное уточнение декларации при расхождении данных
+- сверку объёма по рейсу до отгрузки
+- оформляем, даже если своей декларации у вас нет
 Рутинный ЭСД выходит за 15 минут с момента ваших данных. Разбор расхождений дольше, скажу срок сразу.
-Доверенность в системе, доступ к паролю не нужен.
+Своя декларация и доступ в систему вам не нужны, документ приходит готовым.
 Напишите свою ситуацию, отвечу что можно сделать и за какой срок.</t>
         </is>
       </c>
@@ -19227,14 +19227,14 @@
       <c r="F89" t="inlineStr">
         <is>
           <t>ЭСД и QR код на рейс, оформляем через ФГИС ЛК.
-Машина под погрузкой, покупатель ждёт, а сопроводительного документа нет. При действующей декларации и нормальных остатках это 15 минут после ваших данных по рейсу.
+Машина под погрузкой, покупатель ждёт, а сопроводительного документа нет. Обычно это 15 минут после ваших данных по рейсу.
 Сосна и ель, кругляк 6 метров, диаметр от 20 см.
 Что делаем:
 - ЭСД и QR код водителю на каждую машину
 - проверку остатков и данных декларации перед отгрузкой
-- законное уточнение декларации, если фактический объём отличается
-Если данные расходятся, сначала разбираемся с декларацией, срок обсуждаем отдельно.
-Работаем по доверенности в системе, пароли от вашего кабинета передавать не нужно.
+- берём объём на себя, когда свои остатки не подходят
+Если случай нестандартный, скажу срок отдельно, до начала работы.
+Оформляем со своей стороны. Вам не нужны ни кабинет, ни электронная подпись.
 Напишите свою ситуацию, отвечу что можно сделать и за какой срок.</t>
         </is>
       </c>
@@ -19367,9 +19367,9 @@
 В работе:
 - ЭСД и QR код водителю
 - сверка фактических объёмов с данными в системе
-- законное уточнение декларации, если данные разошлись
+- закрываем рейс, если по своим документам не проходит
 Сроки честные: рутинный ЭСД около 15 минут с момента, когда пришли данные по машине. Разбор расхождений занимает больше, обычно рабочий день.
-Оформляем доверенность в системе, логин и пароль от кабинета не запрашиваю.
+Работаем так, что от вас нужны только данные по рейсу. Своя декларация не требуется.
 Опишите, что у вас происходит, скажу с чего начать.</t>
         </is>
       </c>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_1.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_3.png</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_3.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_3.png</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_3.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_3.png</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_3.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_3.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_3.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_1.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_3.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_2.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_3.png</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_1.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_1.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_3.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_1.png | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_3.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -6848,6 +6848,381 @@
       <c r="AD18" t="inlineStr">
         <is>
           <t>2026-07-25T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6654494961</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/3.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>250</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Документы на лес в ФГИС ЛК, ЭСД и QR код</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Есть лес, а документов на него нет? Это к нам. Оформим происхождение так, чтобы вы спокойно продавали и возили.&lt;br&gt;Проведём ваш объём через ФГИС ЛК по договору купли-продажи, дадим ЭСД и QR на перевозку, поставим на учёт, сделаем декларацию и отчёт 1-ИЛ.&lt;br&gt;От вас порода и кубатура, остальное соберём сами. Удалённо, ИП и ООО.&lt;br&gt;Опишите, сколько леса и откуда, посчитаем сроки и цену.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Кировская обл., Вятские Поляны, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-09-05T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1481923475</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/3.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформление в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Лес лежит, покупатель есть, а сделка не идёт, потому что документов ноль. Знакомо? Мы эту стену убираем.&lt;br&gt;Подтвердим происхождение через наш объём и договор купли-продажи, сделаем ЭСД и QR, поставим кубы на учёт, поможем с декларацией и 1-ИЛ.&lt;br&gt;Всё удалённо, Новгородская область и соседи, без беготни по инстанциям.&lt;br&gt;Киньте в чат, что за лес и сколько, подскажем как оформить.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Чудово, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-09-06T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-08-07T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8194168577</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/3.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9990</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Документы на древесину ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Достался лес, а откуда он по бумагам взялся, непонятно даже вам. Для ФГИС это проблема, для нас обычная задача.&lt;br&gt;Оформим происхождение через наш объём и договор, поставим на учёт, выпустим ЭСД, QR, сделаем декларацию и отчёт 1-ИЛ. Под ключ, от и до.&lt;br&gt;Карелия, работаем удалённо с ИП и ООО.&lt;br&gt;Напишите, что за древесина и в каком объёме, дадим план и цену.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Олонец, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-09-07T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ90"/>
+  <dimension ref="A1:AJ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -19470,6 +19845,656 @@
       <c r="AJ90" t="inlineStr">
         <is>
           <t>2026-07-28T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7393214976</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, документы ФГИС ЛК, ЭСД QR</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Есть сосна, а документов на неё нет? Сам лес нам не нужен, наша работа сделать на него полный пакет в ФГИС ЛК.&lt;br&gt;Оформим ваш объём через договор купли-продажи, дадим ЭСД и QR на перевозку, проведём декларацию и 1-ИЛ. После этого лес спокойно едет и продаётся.&lt;br&gt;Удалённо, по всей стране, ИП и юрлица. От вас цифры, остальное на нас.&lt;br&gt;Напишите объём, прикинем сроки и цену.&lt;br&gt;По теме сосна, пиловочник, хвойный кругляк, объём любой.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/3.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Братск, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>2026-09-05T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4382774059</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Сосна доска, документы ФГИС ЛК, ЭСД и QR код</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Напилили доски, а бумаг на неё нет, и покупатель уже нервничает. Пилораму держите свою, документы сделаем мы.&lt;br&gt;Проведём объём в ФГИС ЛК по договору, выпустим ЭСД и QR, оформим декларацию, 1-ИЛ и коды ОКПД2. Груз уедет чистым.&lt;br&gt;Работаем удалённо, Красноярск и весь край.&lt;br&gt;Отпишите объём и сечения, назовём цену и срок.&lt;br&gt;По теме пиломатериал, доска обрезная сосна, любые размеры.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/3.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Красноярский край, Красноярск, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>11000</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Доска</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>2026-09-06T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8757513433</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Лиственница брус, документы ФГИС ЛК, ЭСД QR</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Лиственница есть, а по документам пусто. Продать такую боязно, вывезти тем более. Берём эту часть на себя.&lt;br&gt;Оформим происхождение через наш объём и договор, дадим ЭСД и QR, проведём декларацию и 1-ИЛ. На любой объём, хоть небольшой, хоть вагонами.&lt;br&gt;Удалённо, Пермский край и дальше, ИП и ООО.&lt;br&gt;Опишите, что и сколько, посчитаем стоимость.&lt;br&gt;По теме лиственница, брус, доска, пиломатериал.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/3.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Пермский край, Соликамск, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Брус</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>2026-09-06T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>9218798416</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Берёза баланс, документы ФГИС ЛК, ЭСД QR код</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Берёзовый баланс собрали, а комбинат без документов его не примет. Сделаем так, чтобы приняли.&lt;br&gt;Подтвердим объём через договор, заведём в ФГИС ЛК, выпустим ЭСД и QR, оформим декларацию и 1-ИЛ. Лес поедет по закону.&lt;br&gt;Киров и область, всё удалённо.&lt;br&gt;Напишите объём и куда сдаёте, дадим цену и сроки.&lt;br&gt;По теме берёза, баланс, лиственный кругляк.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/3.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Кировская обл., Киров, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>2026-09-07T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3819625066</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ель кругляк, документы ФГИС ЛК, ЭСД и QR код</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ель и кругляк есть в наличии, а документов на них нет. Без бумаг это мёртвый груз. Оживим.&lt;br&gt;Оформим ваш объём через договор купли-продажи, дадим ЭСД и QR, проведём декларацию и отчёт 1-ИЛ. Покупатель получит лес с полным пакетом.&lt;br&gt;Вологодская область, работаем удалённо.&lt;br&gt;Скиньте объём и станцию, посчитаем.&lt;br&gt;По теме ель, пиловочник, хвойный кругляк.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/3.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Череповец, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>2026-09-07T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20866,7 +21891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -22412,6 +23437,256 @@
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-07-25T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2153018262</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/3.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>990</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Оформление древесины в ФГИС ЛК, ЭСД на лес</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Купили древесину, а по бумагам её как будто и нет. Ни продать, ни вывезти, зато штраф словить легко. Помогаем это закрыть.&lt;br&gt;Оформляем ваш объём официально через договор, заводим в ФГИС ЛК, выпускаем ЭСД, привязываем к декларации и МСД. На выходе лес белый.&lt;br&gt;Работаем по вашим данным или подключаемся к учётке. Коми и рядом.&lt;br&gt;Расскажите ситуацию в сообщениях, разберём по-человечески.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Республика Коми, Койгородок, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-09-06T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5312403632</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/3.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4990</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Закрытие расхождений по лесу в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Заготовили или взяли леса больше, чем есть по документам, и излишек висит серым. Мы его выведем в белую.&lt;br&gt;Закроем разницу через договор, проведём объём в ФГИС ЛК, дадим ЭСД и QR на каждую машину, подтянем ОКПД2 и склад.&lt;br&gt;От вас порода и кубы, дальше наша забота. Удалённо, ИП и юрлица.&lt;br&gt;Скиньте объём и куда возите, посчитаем.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Кириши, ул. Ленина, 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-09-06T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -6859,7 +6859,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -7092,12 +7092,12 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-06T12:00:00+03:00</t>
+          <t>2026-09-06T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2026-08-07T14:00:00+03:00</t>
+          <t>2026-08-07T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-07T10:00:00+03:00</t>
+          <t>2026-09-07T02:30:00+03:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2026-08-08T12:00:00+03:00</t>
+          <t>2026-08-08T04:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-06T10:00:00+03:00</t>
+          <t>2026-09-06T02:30:00+03:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>2026-08-07T12:00:00+03:00</t>
+          <t>2026-08-07T04:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-06T14:00:00+03:00</t>
+          <t>2026-09-06T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>2026-08-07T16:00:00+03:00</t>
+          <t>2026-08-07T07:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20344,7 +20344,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-07T08:00:00+03:00</t>
+          <t>2026-09-07T01:00:00+03:00</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>2026-08-08T10:00:00+03:00</t>
+          <t>2026-08-08T03:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-07T12:00:00+03:00</t>
+          <t>2026-09-07T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2026-08-08T14:00:00+03:00</t>
+          <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -23556,12 +23556,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-06T08:00:00+03:00</t>
+          <t>2026-09-06T01:00:00+03:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-07T10:00:00+03:00</t>
+          <t>2026-08-07T03:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-06T16:00:00+03:00</t>
+          <t>2026-09-06T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-07T18:00:00+03:00</t>
+          <t>2026-08-07T09:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -20059,7 +20059,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Доска</t>
+          <t>Лес-кругляк</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Брус</t>
+          <t>Лес-кругляк</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -7223,6 +7223,381 @@
       <c r="AD21" t="inlineStr">
         <is>
           <t>2026-08-08T04:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2944694864</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/3.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Закрываем расхождения в ФГИС ЛК по лесу</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Приводим в порядок учёт, когда остатки в системе не сходятся с фактом и отгрузки встали.&lt;br&gt;Работаем в четыре шага.&lt;br&gt;Первое. Смотрим вашу учётную запись или выгрузку, сверяем баланс с реальным остатком, поднимаем сделки за период.&lt;br&gt;Второе. Находим причину. Обычно это дубли сделок, недосписанные объёмы, непроведённые отгрузки или ошибка контрагента.&lt;br&gt;Третье. Закрываем разницу. Оформляем договор купли-продажи через свой объём и ставим недостающие кубы на баланс.&lt;br&gt;Четвёртое. Проверяем, что отгрузки пошли и декларация встаёт.&lt;br&gt;Первый шаг делаем до оплаты. Если случай не наш, скажем прямо и не будем тянуть деньги.&lt;br&gt;Опишите, на чём именно встало, посмотрим.&lt;br&gt;Расхождения ФГИС ЛК, излишки древесины, баланс, блокировка отгрузки, лесной учёт.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Тихвин, ул. Карла Маркса, 10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-09-12T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2026-08-13T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8255033246</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/3.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>700</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Сопровождение ФГИС ЛК, работа по месяцам</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ведём ФГИС ЛК постоянно, а не от случая к случаю. Формат простой: вы работаете, мы держим документы в порядке.&lt;br&gt;Что входит в месяц:&lt;br&gt;оформление ЭСД и QR на каждую машину без ограничения по количеству;&lt;br&gt;проведение сделок и объёмов в системе;&lt;br&gt;сверка остатков, чтобы не копились расхождения;&lt;br&gt;лесная декларация и отчёт 1-ИЛ в срок;&lt;br&gt;ответы на вопросы по учёту в рабочее время.&lt;br&gt;Кому подходит. Тем, кто отгружает регулярно и не хочет держать отдельного человека под документы. Один рейс в неделю или десять в день, разницы в подходе нет.&lt;br&gt;Начать можно с разовой задачи, а дальше перейти на ведение, если понравится, как работаем.&lt;br&gt;Напишите, сколько машин в месяц отгружаете, посчитаем.&lt;br&gt;Сопровождение ФГИС ЛК, ведение учёта древесины, ЭСД, QR код, отчёт 1-ИЛ, декларация.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Орловская обл., Мценск, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-09-14T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9305700055</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n15/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n15/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n15/3.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Документы на лес для юрлиц и тендеров</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Готовим документацию по древесине для юрлиц: под сделку, под тендер, под проверку.&lt;br&gt;С чем обычно приходят.&lt;br&gt;Заказчик просит подтвердить происхождение древесины по контракту.&lt;br&gt;Для участия в закупке нужен пакет по лесу, а его никто в компании не вёл.&lt;br&gt;Пришёл запрос от контролирующих, и надо привести учёт в соответствие.&lt;br&gt;Что делаем: оформляем происхождение договором, ставим объём на баланс в ФГИС ЛК, выпускаем ЭСД и QR на отгрузки, подтягиваем ОКПД2, готовим декларацию и отчёт 1-ИЛ.&lt;br&gt;Работаем по договору с оплатой на расчётный счёт, закрывающие документы предоставляем.&lt;br&gt;Опишите, что именно требует ваш заказчик или проверяющий, соберём пакет под требование.&lt;br&gt;Документы на лес для юрлиц, тендер, закупка, контракт, ФГИС ЛК, ЭСД, ОКПД2, отчётность.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Тульская обл., Алексин, ул. Героев-Алексинцев, 3</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026-08-16T18:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7875,7 +8250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ95"/>
+  <dimension ref="A1:AJ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -20495,6 +20870,1306 @@
       <c r="AJ95" t="inlineStr">
         <is>
           <t>2026-08-08T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>5256328121</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Доска обрезная, документы ФГИС ЛК и ЭСД</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Оформляем документы на пиломатериал и на сырьё, из которого он напилен.&lt;br&gt;Простыми словами, что вообще требуется.&lt;br&gt;ФГИС ЛК. Государственная система учёта древесины. Пока объём в ней не числится, для государства его нет.&lt;br&gt;ЭСД. Электронный документ на конкретную перевозку. Оформляется до выезда машины.&lt;br&gt;QR-код. То, что показывают на проверке. Инспектор сканирует и видит, откуда груз.&lt;br&gt;ОКПД2. Код продукции, его просят покупатели-юрлица.&lt;br&gt;1-ИЛ и декларация. Отчётность за период, сдают те, у кого есть участки или сделки с лесом.&lt;br&gt;Всё это делаем за вас. От вас нужны объём, сечения и регион.&lt;br&gt;Не знаете, что именно требуется в вашем случае, напишите, разберём бесплатно и без обязательств.&lt;br&gt;Доска обрезная и необрезная, пиломатериал, сосна, ель, ФГИС ЛК, ЭСД, QR код, ОКПД2.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/3.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Кировская обл., Омутнинск, ул. Коковихина, 2</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>2026-09-12T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1582439801</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Горбыль и дрова, ЭСД и QR на перевозку</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Делаем документы на горбыль, дрова и отходы пиления.&lt;br&gt;Обращайтесь, если про вас хотя бы один пункт:&lt;br&gt;древесина куплена у населения и подтвердить происхождение нечем;&lt;br&gt;котельная или покупатель просят полный пакет;&lt;br&gt;машина готова к выезду, а ЭСД никто не выписывает;&lt;br&gt;в ФГИС ЛК цифры не сходятся с остатком;&lt;br&gt;надо сдавать декларацию и 1-ИЛ, а заниматься некому.&lt;br&gt;В любом из случаев делаем одно: договор, учёт объёма, ЭСД, QR, отчётность.&lt;br&gt;Горбыль и дрова возят часто и партиями, поэтому обычно ставим клиента на сопровождение и закрываем каждую машину.&lt;br&gt;Напишите, какой пункт ваш, с него и начнём.&lt;br&gt;Горбыль, дрова, отходы пиления, дровяник, ЭСД, QR код, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n07/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n07/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n07/3.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Республика Коми, Прилузский р-н, с. Объячево, ул. Мира, 20</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>2026-09-13T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>2026-08-14T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5077954476</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Пиломатериал для стройки, документы ФГИС</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Оформляем документы на пиломатериал для строительных компаний и подрядчиков.&lt;br&gt;Ситуация типовая. Материал куплен у пилорамы или на базе, объект идёт, а бухгалтерия заказчика требует закрывающие документы и подтверждение происхождения древесины. Без них объём не принимают и оплату задерживают.&lt;br&gt;Что готовим:&lt;br&gt;договор купли-продажи на объём;&lt;br&gt;проведение древесины через ФГИС ЛК;&lt;br&gt;ЭСД и QR на доставку до объекта;&lt;br&gt;коды ОКПД2 для акта и счёта.&lt;br&gt;Подходит для подряда, госзаказа и обычной поставки юрлицу.&lt;br&gt;Работаем удалённо, Московская область и соседние регионы, объём от одной машины.&lt;br&gt;Напишите объём и что требует заказчик, соберём под его требования.&lt;br&gt;Пиломатериал, доска, брус, стройка, подряд, закрывающие документы, ФГИС ЛК, ЭСД, ОКПД2.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/3.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Московская обл., Шатура, Спортивный пр-д, 4</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>2026-09-13T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3355650359</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, ЭСД и QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Оформляем документы на пиловочник. Сам лес остаётся у вас, мы делаем бумаги, чтобы его можно было везти и продавать.&lt;br&gt;Отвечаю сразу на частые вопросы.&lt;br&gt;Вы продаёте лес? Нет, мы занимаемся документацией на чужую древесину.&lt;br&gt;Лес куплен без документов, поможете? Да, это наш основной случай. Происхождение подтверждаем договором через свой объём.&lt;br&gt;Сколько ждать ЭСД? В течение дня. Если рейс срочный, сделаем быстрее.&lt;br&gt;Надо куда-то ехать? Нет, всё удалённо. Работаем с ИП и с ООО.&lt;br&gt;Что будет на руках? Договор, объём в ФГИС ЛК, ЭСД и QR на рейс. По необходимости декларация и отчёт 1-ИЛ.&lt;br&gt;Сколько стоит? Зависит от объёма, называем до начала работы.&lt;br&gt;Напишите кубатуру и маршрут, посчитаем.&lt;br&gt;Сосна пиловочник, хвойный лес, ЭСД, QR код, ФГИС ЛК, документы на древесину.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/3.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Калужская обл., Жиздра, ул. Володарского, 5</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>2026-09-13T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4393089394</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Лиственница пиловочник, документы ФГИС</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Оформляем документы на древесину, включая объёмы, которые не проходят по бумагам.&lt;br&gt;Скажу прямо, потому что с этим приходят чаще всего. У большинства заготовителей набегает разница между тем, что лежит на площадке, и тем, что учтено. Причины простые: пересортица, замер на глаз, докупили у соседа, часть увезли без оформления.&lt;br&gt;Пока лес лежит, это никого не волнует. Проблемы начинаются на отгрузке и на отчётности.&lt;br&gt;Что мы делаем. Закрываем разницу договором купли-продажи через свой объём. Кубы встают на баланс в ФГИС ЛК. Дальше по ним спокойно выпускаются ЭСД и QR.&lt;br&gt;Работаем без лишних вопросов. Задача простая: чтобы у вас всё сходилось и отгрузки шли.&lt;br&gt;Опишите ситуацию своими словами, скажем честно, решается или нет.&lt;br&gt;Лиственница пиловочник, излишки древесины, расхождения ФГИС ЛК, ЭСД, QR код.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n09/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n09/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n09/3.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Тверская обл., Нелидово, ул. Строителей, 3</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>2026-09-14T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2054813701</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Оцилиндрованное бревно, документы ФГИС</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Делаем документы на оцилиндрованное бревно, профилированный брус и домокомплекты.&lt;br&gt;Знакомая ситуация. Заказчик берёт сруб, всё согласовано. Потом его бухгалтерия просит документы на древесину, и сделка виснет. Особенно если покупатель юрлицо и ему нужен закрывающий пакет.&lt;br&gt;Мы это закрываем:&lt;br&gt;оформляем происхождение сырья договором;&lt;br&gt;проводим объём через ФГИС ЛК;&lt;br&gt;даём ЭСД и QR на доставку комплекта;&lt;br&gt;подтягиваем коды ОКПД2 под сделку.&lt;br&gt;Возите постоянно, поставим на сопровождение и будем закрывать каждую отгрузку.&lt;br&gt;Напишите объём и куда идёт комплект, посчитаем.&lt;br&gt;Оцилиндрованное бревно, профилированный брус, домокомплект, сруб, ФГИС ЛК, ЭСД, QR код, ОКПД2.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/3.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Брянская обл., Унеча, ул. Октябрьская, 7</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>2026-08-15T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4806783818</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы ФГИС ЛК, ЭСД</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Оформляем полный пакет документов на пиловочник.&lt;br&gt;Коротко о том, чем рискует тот, кто возит без бумаг.&lt;br&gt;Рейс без ЭСД. Машину задерживают, груз изымают до выяснения, штраф доходит до 500 тысяч рублей.&lt;br&gt;Продажа без подтверждённого происхождения. Сделку могут признать сомнительной, и покупатель попадёт следом.&lt;br&gt;Расхождение в системе. Отгрузки блокируются, а разбирать это задним числом дороже, чем оформить сразу.&lt;br&gt;Что делаем мы: договор на объём, постановка кубов в ФГИС ЛК, ЭСД и QR на каждую отгрузку, декларация и отчёт 1-ИЛ.&lt;br&gt;Работаем по всей стране удалённо, объём от одной машины.&lt;br&gt;Напишите кубатуру и маршрут, посчитаем.&lt;br&gt;Ель пиловочник, хвоя, ЭСД, QR код, ФГИС ЛК, штраф за перевозку леса.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/3.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Республика Коми, Корткеросский р-н, с. Корткерос, ул. Советская, 6</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7075063855</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Брус и доска, ЭСД на перевозку, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Документы на брус, доску и сырьё под них. Коротко и по делу.&lt;br&gt;Что делаем: договор на объём, учёт в ФГИС ЛК, ЭСД, QR-код, ОКПД2, декларация, отчёт 1-ИЛ.&lt;br&gt;Срок: ЭСД на рейс в течение дня, срочный от 15 минут. Полный пакет от одного дня.&lt;br&gt;Объём: от одной машины, верхней границы нет.&lt;br&gt;Где работаем: вся Россия, удалённо.&lt;br&gt;С кем: ИП и юрлица, по договору, оплата на расчётный счёт.&lt;br&gt;Зачем это: без сопроводительных документов рейс стоит до 500 тысяч штрафа, а груз задерживают.&lt;br&gt;Что нужно от вас: объём, сечения, маршрут.&lt;br&gt;Пришлите эти три пункта, ответим ценой и сроком.&lt;br&gt;Брус, доска обрезная, пиломатериал, ЭСД, QR код, ФГИС ЛК, ОКПД2.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/2.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/3.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Калужская обл., Людиново, ул. Крупской, 5</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>2026-09-15T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>2026-08-16T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7235664895</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Дрова колотые, документы ФГИС ЛК и ЭСД</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Делаем документы на дрова и низкосортную древесину, если купили их без бумаг.&lt;br&gt;Когда это нужно. Взяли лес у населения. Часть со своей делянки, часть по случаю. Везёте в котельную или частнику, а подтвердить происхождение нечем.&lt;br&gt;Что вы получаете:&lt;br&gt;договор купли-продажи на ваш объём;&lt;br&gt;кубы, заведённые в ФГИС ЛК;&lt;br&gt;ЭСД и QR-код на каждую машину;&lt;br&gt;декларацию и отчёт 1-ИЛ, если они на вас.&lt;br&gt;Как проходит. Вы пишете породу, кубатуру и куда идёт машина. Мы всё оформляем и отдаём готовые документы. Приезжать никуда не надо.&lt;br&gt;Объём любой, от одной машины. Работаем с ИП и с ООО по всей стране.&lt;br&gt;Напишите объём, назовём цену и срок.&lt;br&gt;Дрова колотые, берёза, осина, дровяник, документы на лес, ЭСД, QR код, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/3.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Московская обл., Егорьевск, ул. Советская, 6</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>2026-08-16T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4316812338</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвойный, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Оформляем документы для пилорам и тех, кто перепродаёт пиломатериал.&lt;br&gt;Ситуация обычно одна. Сырьё берут по-разному: часть у местных, часть по случаю. Продукция готова, а покупатель просит бумаги и упирается.&lt;br&gt;Что входит в работу:&lt;br&gt;договор купли-продажи на объём сырья;&lt;br&gt;учёт в ФГИС ЛК;&lt;br&gt;ЭСД и QR на отгрузку;&lt;br&gt;коды ОКПД2 под сделку;&lt;br&gt;декларация и отчёт 1-ИЛ по необходимости.&lt;br&gt;Объём от одной фуры до вагонных партий. Всё дистанционно, без поездок и живых подписей.&lt;br&gt;Напишите объём и сечения, посчитаем.&lt;br&gt;Пиломатериал, доска, брус, горбыль, сосна, ель, ФГИС ЛК, ЭСД, ОКПД2.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Бокситогорск, ул. Заводская, 4</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>2026-09-16T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -21891,7 +23566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -23687,6 +25362,381 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-07T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2337851497</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Лесная декларация и отчёт 1-ИЛ, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ведём отчётность по лесу за вас: декларация, отчёт 1-ИЛ, сведения о сделках.&lt;br&gt;Что и когда сдаётся, если коротко.&lt;br&gt;Лесная декларация подаётся заранее, до начала работ на участке, и потом корректируется по факту.&lt;br&gt;Отчёт 1-ИЛ сдаётся за период по фактически заготовленному объёму.&lt;br&gt;Сведения о сделках вносятся в ФГИС ЛК в срок, иначе объём повисает и отгрузки блокируются.&lt;br&gt;Мы готовим и подаём всё перечисленное, правим учёт, чтобы отчёт сошёлся с фактом, и параллельно закрываем текущие отгрузки через ЭСД и QR.&lt;br&gt;Можно разово, чтобы закрыть горящий период. Можно на постоянное сопровождение, чтобы больше об этом не думать.&lt;br&gt;Напишите, что у вас с отчётностью и какие сроки горят, назовём стоимость.&lt;br&gt;Лесная декларация, отчёт 1-ИЛ, ФГИС ЛК, лесной учёт, МСД, сведения о сделках.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Псковская обл., Великие Луки, пр-т Ленина, 10</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-09-13T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-14T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2910390390</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n10/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n10/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n10/3.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса за 15 минут</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Оформляем QR-код и ЭСД на перевозку древесины. Срочно, в день обращения.&lt;br&gt;От вас три вещи: порода, кубатура, маршрут.&lt;br&gt;Дальше наша работа. Проводим объём через ФГИС ЛК по договору, выпускаем ЭСД, отдаём QR-код.&lt;br&gt;При полных данных укладываемся в 15 минут. Если чего-то не хватает, скажем сразу, а не через час.&lt;br&gt;Пишите в любое время, отвечаем вечером и в выходные. Лес возят не по графику, мы это понимаем.&lt;br&gt;Возите постоянно, закрепим за вами человека и будем оформлять каждую машину по мере выхода.&lt;br&gt;Цена зависит от объёма и срочности, называем до начала работы.&lt;br&gt;Скиньте маршрут и кубатуру, начнём.&lt;br&gt;QR код на лес, ЭСД, перевозка древесины, сопроводительные документы, срочно, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Старая Русса, ул. Минеральная, 5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-09-15T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-16T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>9271513301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n13/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n13/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n13/3.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>990</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Документы на древесину ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Берём на себя всю документацию по древесине, от происхождения до отчётности.&lt;br&gt;Сравните, сколько это стоит вам по времени.&lt;br&gt;Своими силами. Разобраться в требованиях к происхождению. Найти, через кого легально провести объём. Получить и настроить КЭП. Освоить систему. Не ошибиться в сделке. Потом выпускать ЭСД на каждую машину и не сорвать отчётность. В первый раз это недели.&lt;br&gt;Через нас. Вы называете породу, объём и регион. Получаете договор, кубы на балансе в ФГИС ЛК, ЭСД и QR на отгрузки, декларацию и отчёт 1-ИЛ. Дальше просто пишете, когда выходит очередная машина.&lt;br&gt;Свой объём 300 000 кубов, поэтому подтверждение происхождения не упирается в поиск поставщика.&lt;br&gt;Берём и разовую задачу, и постоянное ведение. ИП и юрлица, вся страна, удалённо.&lt;br&gt;Опишите, что за древесина и какой объём, дадим план и цену.&lt;br&gt;Документы на древесину, оформление леса под ключ, ФГИС ЛК, происхождение, ЭСД, QR код, КЭП.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ярославская обл., Рыбинск, ул. Крестовая, 20</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-09-16T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -14073,6 +14073,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>2026-08-18T09:00:00+03:00</t>
+        </is>
+      </c>
       <c r="AF43" t="inlineStr">
         <is>
           <t>belpool.1@gmail.com</t>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-22T10:00:00+03:00</t>
+          <t>2026-09-21T09:37:38+03:00</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-21T10:00:00+03:00</t>
+          <t>2026-09-20T09:36:07+03:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-24T10:00:00+03:00</t>
+          <t>2026-09-23T09:37:51+03:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-24T13:00:00+03:00</t>
+          <t>2026-09-23T12:09:35+03:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-05T08:00:00+03:00</t>
+          <t>2026-09-05T13:07:37+03:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-06T04:00:00+03:00</t>
+          <t>2026-09-06T03:06:05+03:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-07T02:30:00+03:00</t>
+          <t>2026-09-07T01:35:41+03:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-12T16:00:00+03:00</t>
+          <t>2026-09-12T15:06:07+03:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-14T05:30:00+03:00</t>
+          <t>2026-09-14T04:38:14+03:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-15T16:00:00+03:00</t>
+          <t>2026-09-15T15:06:23+03:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-08-14T14:33:49+03:00</t>
+          <t>2026-09-13T14:37:02+03:00</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-08-15T03:00:00+03:00</t>
+          <t>2026-09-14T02:36:45+03:00</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-08-15T05:30:00+03:00</t>
+          <t>2026-09-14T05:08:02+03:00</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-08-15T08:00:00+03:00</t>
+          <t>2026-09-14T07:38:08+03:00</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-08-15T10:30:00+03:00</t>
+          <t>2026-09-14T10:07:14+03:00</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-08-15T13:00:00+03:00</t>
+          <t>2026-09-14T12:37:12+03:00</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-08-15T15:30:00+03:00</t>
+          <t>2026-09-14T15:06:49+03:00</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-08-15T18:00:00+03:00</t>
+          <t>2026-09-14T17:35:57+03:00</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-08-16T03:00:00+03:00</t>
+          <t>2026-09-15T02:35:43+03:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-08-16T05:30:00+03:00</t>
+          <t>2026-09-15T04:37:05+03:00</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-08-16T08:00:00+03:00</t>
+          <t>2026-09-15T07:37:30+03:00</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-08-16T10:30:00+03:00</t>
+          <t>2026-09-15T10:07:04+03:00</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-08-16T13:00:00+03:00</t>
+          <t>2026-09-15T12:36:34+03:00</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-08-16T15:30:00+03:00</t>
+          <t>2026-09-15T15:06:23+03:00</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-08-16T18:00:00+03:00</t>
+          <t>2026-09-15T17:36:49+03:00</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-08-20T13:00:00+03:00</t>
+          <t>2026-09-19T12:37:38+03:00</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-08-20T15:30:00+03:00</t>
+          <t>2026-09-19T15:07:21+03:00</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-08-21T07:00:00+03:00</t>
+          <t>2026-09-20T06:36:02+03:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-08-21T13:00:00+03:00</t>
+          <t>2026-09-20T12:08:18+03:00</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-08-22T04:00:00+03:00</t>
+          <t>2026-09-21T03:35:34+03:00</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-08-22T07:00:00+03:00</t>
+          <t>2026-09-21T06:37:22+03:00</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-08-23T04:00:00+03:00</t>
+          <t>2026-09-22T03:35:56+03:00</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-08-23T07:00:00+03:00</t>
+          <t>2026-09-22T06:37:13+03:00</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-08-23T13:00:00+03:00</t>
+          <t>2026-09-22T12:37:09+03:00</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-08-24T04:00:00+03:00</t>
+          <t>2026-09-23T03:35:57+03:00</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-08-24T07:00:00+03:00</t>
+          <t>2026-09-23T06:37:29+03:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-08-28T14:00:00+03:00</t>
+          <t>2026-09-27T16:06:59+03:00</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-08-28T18:00:00+03:00</t>
+          <t>2026-09-27T15:37:07+03:00</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-08-29T06:00:00+03:00</t>
+          <t>2026-09-28T03:36:14+03:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-08-29T14:00:00+03:00</t>
+          <t>2026-09-28T11:37:20+03:00</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-08-29T18:00:00+03:00</t>
+          <t>2026-09-28T15:36:26+03:00</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-08-30T06:00:00+03:00</t>
+          <t>2026-09-29T03:36:00+03:00</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-08-30T10:00:00+03:00</t>
+          <t>2026-09-29T15:06:26+03:00</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-08-30T14:00:00+03:00</t>
+          <t>2026-09-29T15:06:25+03:00</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-08-30T18:00:00+03:00</t>
+          <t>2026-09-29T15:36:38+03:00</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-08-31T06:00:00+03:00</t>
+          <t>2026-09-30T03:39:32+03:00</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-08-31T10:00:00+03:00</t>
+          <t>2026-09-30T07:43:23+03:00</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-08-31T18:00:00+03:00</t>
+          <t>2026-08-31T15:06:35+03:00</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-08-27T13:15:00+03:00</t>
+          <t>2026-09-26T11:38:23+03:00</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-05T10:00:00+03:00</t>
+          <t>2026-09-19T13:06:27+03:00</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-06T02:30:00+03:00</t>
+          <t>2026-09-06T01:35:36+03:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-06T05:30:00+03:00</t>
+          <t>2026-09-06T04:36:37+03:00</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-07T01:00:00+03:00</t>
+          <t>2026-09-07T00:05:22+03:00</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-12T14:00:00+03:00</t>
+          <t>2026-09-12T13:07:34+03:00</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-13T04:00:00+03:00</t>
+          <t>2026-09-13T03:05:59+03:00</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-13T06:00:00+03:00</t>
+          <t>2026-09-13T05:07:57+03:00</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-14T03:30:00+03:00</t>
+          <t>2026-09-14T02:36:51+03:00</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-14T07:30:00+03:00</t>
+          <t>2026-09-14T06:37:09+03:00</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-14T10:00:00+03:00</t>
+          <t>2026-09-14T09:07:28+03:00</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:00+03:00</t>
+          <t>2026-09-21T15:36:36+03:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-23T16:00:00+03:00</t>
+          <t>2026-09-22T15:36:26+03:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-24T16:00:00+03:00</t>
+          <t>2026-09-24T12:37:01+03:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-06T01:00:00+03:00</t>
+          <t>2026-09-06T00:06:00+03:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-06T07:00:00+03:00</t>
+          <t>2026-09-06T06:08:27+03:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -25486,7 +25486,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-13T08:30:00+03:00</t>
+          <t>2026-09-13T07:38:24+03:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-15T04:30:00+03:00</t>
+          <t>2026-09-15T03:35:46+03:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-16T07:00:00+03:00</t>
+          <t>2026-09-16T06:07:40+03:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -20854,7 +20854,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-07T04:00:00+03:00</t>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-13T15:30:00+03:00</t>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-15T06:30:00+03:00</t>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-15T09:00:00+03:00</t>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-16T05:00:00+03:00</t>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -7598,6 +7598,256 @@
       <c r="AD24" t="inlineStr">
         <is>
           <t>2026-08-16T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6184209749</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/bg_barn_hay.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p04.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Документы на лес и пиломатериалы, учёт ФГИС</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ведём документы на лес и пиломатериалы, в том числе на древесину с земель сельхозназначения.&lt;br&gt;Помогаем навести порядок целиком: завести объём в государственную систему учёта, оформить перевозку на каждую машину, получить QR код для проверки, сдать декларацию и годовую отчётность, разобраться со складским учётом остатков.&lt;br&gt;Берём и сложные истории. Партия уже уехала без бумаг, объёмы по документам не сходятся с фактом, система не пропускает декларацию, налоговая или лесничество задают вопросы.&lt;br&gt;Подскажем и куда пристроить объём, если продавать самому не хочется, у нас свой опт.&lt;br&gt;Первый разбор ситуации бесплатный, просто напишите как есть.&lt;br&gt;Кругляк, пиломатериалы, пиловочник, доска, брус.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Тверская обл., Ржев, ул. Ленина, 21</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5884126293</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/bg04.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d08.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s11.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>350</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Пиломатериалы и кругляк, оформление документов</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ведём документы на кругляк и пиломатериалы, включая древесину с земель сельхозназначения.&lt;br&gt;Объясняю по-простому, что обычно требуется. Сначала объём должен появиться в государственной системе учёта, иначе для государства этой древесины нет. Дальше на неё выпускаются документы на перевозку: свой электронный документ на каждую машину и QR код, который проверяют на посту. Отдельно идёт отчётность за период и коды на продукцию, которые спрашивают покупатели-юрлица.&lt;br&gt;Разбираем и запущенные случаи: партия уехала без бумаг, объёмы по документам не сходятся с фактом, система не пропускает декларацию.&lt;br&gt;Работаем с организациями, ИП и частниками по всей стране удалённо.&lt;br&gt;Первый разбор ситуации бесплатный, просто опишите как есть.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Псковская обл., Опочка, Красноармейская ул., 8</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-10-03T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2026-09-03T16:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ105"/>
+  <dimension ref="A1:AJ119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -22175,6 +22425,1826 @@
       <c r="AJ105" t="inlineStr">
         <is>
           <t>2026-08-17T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7499281521</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, документы и QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Помогаем оформить документы на лес, который вырос и срублен на сельхозземле. Ситуация обычная: древесина лежит, а по бумагам её нет, значит вывезти и продать нельзя.&lt;br&gt;Что мы делаем. Проводим ваш объём через договор купли-продажи от своего леса и заводим его в государственную систему учёта. После этого древесина официально существует, и на неё можно получить всё остальное.&lt;br&gt;Что вы получаете на руки. Электронный документ на каждую машину, чтобы везти груз законно. QR код, который сканирует инспектор на посту. Лесную декларацию и годовой отчёт, если они нужны по вашей ситуации.&lt;br&gt;Берём расчистку под пашню, спил старой лесополосы, самосев на брошенном поле.&lt;br&gt;Если продавать некогда, забираем объём себе, работаем оптом по лесу.&lt;br&gt;Скажите породу, сколько кубов и откуда рейс, посчитаем в тот же день.&lt;br&gt;Сосна кругляк, пиловочник, деловая древесина.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/nb_tractor_field.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s01.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Кировская обл., Слободской, ул. Ленина, 3</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>5630744246</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Сосна кругляк с поля(QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Вологодская область, сосна кругляком с сельхозземли.&lt;br&gt; &lt;br&gt;Делаю QR-коды на перевозку древесины. Каждая машина с лесом едет с электронной накладной из ФГИС ЛК, оформляю её быстро, минут за пятнадцать. Система государственная, документ в ней есть, поэтому проверки проходят без разговоров.&lt;br&gt; &lt;br&gt;Отдельно закрываю случай, когда лес срублен не в лесном фонде, а на поле или в лесополосе. Такой объём тоже надо заводить в систему, иначе его ни увезти, ни продать.&lt;br&gt; &lt;br&gt;Для оформления надо немного: данные машины и водителя, порода, кубатура, откуда и куда рейс. Кидаете в сообщения, получаете документ. Пишите.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl14.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j02.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Никольск, ул. Ленина, 12</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>8742440505</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Сосна кругляк с поля, оформление документов</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Оформляем документы под ключ на сосновый кругляк, срубленный на сельхозземле.&lt;br&gt;Объясняю простыми словами, что вообще требуется. Сначала древесина должна появиться в государственной системе учёта, иначе для государства её не существует. Это делается через договор купли-продажи, мы проводим объём через свой лес.&lt;br&gt;Дальше на этот объём выпускаются документы на перевозку: свой электронный документ на каждую машину и QR код для проверки на посту. Если нужна отчётность за период, декларацию и годовой отчёт тоже готовим.&lt;br&gt;Неважно, лесной участок у вас или обычная пашня, порядок один и тот же.&lt;br&gt;Если с покупателем не сложилось, заберём объём себе, торгуем лесом оптом.&lt;br&gt;Скажите породу и сколько кубов, посчитаем стоимость.&lt;br&gt;Сосна кругляк, пиловочник, деловая древесина.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/sd_field_pile.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p03.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d01.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Псковская обл., Остров, ул. Ленина, 9</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>2026-09-01T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9519971479</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, оформим документы на лес</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Оформляем документы на сосновый пиловочник и другой лес, срубленный на землях сельхозназначения.&lt;br&gt;Многие не знают, что учёт древесины одинаковый и для лесного фонда, и для обычного поля. Если лес вырос на пашне или в полосе вдоль дороги, его всё равно надо провести через государственную систему, иначе на первом посту начнутся вопросы.&lt;br&gt;Мы закрываем это целиком. Оформляем происхождение объёма через договор купли-продажи, заносим партию в систему, готовим сопроводительный документ на каждый рейс и QR код для проверки. Отчётность за период тоже берём на себя.&lt;br&gt;Работаем с хозяйствами, ИП и частниками, по всей стране удалённо, приезжать никуда не надо.&lt;br&gt;Нужен ещё и покупатель, скажите, торгуем лесом оптом сами.&lt;br&gt;Напишите объём и породу, разберём вашу ситуацию бесплатно.&lt;br&gt;Сосна пиловочник, кругляк, баланс, лесоматериалы.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/logs_close.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s03.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d03.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Республика Коми, Сосногорск, ул. Ленина, 7</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>2026-10-01T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>2026-09-01T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>5954622193</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Берёза дрова и баланс, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Помогаем оформить документы на берёзовые дрова и баланс, заготовленные на сельхозугодьях.&lt;br&gt;Берёза с зарастающего поля идёт и на дрова, и на баланс для комбината, но и в том, и в другом случае покупатель попросит документы на происхождение. Без учёта в государственной системе их взять негде.&lt;br&gt;Как решаем. Заводим объём в систему через договор купли-продажи, дальше готовим электронный документ на каждый рейс и QR код для проверки на дороге. Годовую отчётность и декларацию делаем, если требуются.&lt;br&gt;Берём и одну машину, и постоянную вывозку по графику.&lt;br&gt;Есть свой оптовый канал, при желании выкупим объём сами.&lt;br&gt;Пришлите объём и куда везёте, ответим быстро.&lt;br&gt;Берёза дрова, баланс, кругляк, пиловочник, лесоматериалы.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/bg08.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p07.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s10.jpg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Ярославская обл., Данилов, ул. Ленина, 21</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>2026-10-01T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2628527396</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы на вывоз с поля</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Оформляем документы на еловый пиловочник и другой лес, вывозимый с зарастающего поля.&lt;br&gt;Ситуация у всех одинаковая: поле годами не пахали, на нём поднялся нормальный лес, его срубили, а дальше тупик, потому что документов на такую древесину нет ни у кого.&lt;br&gt;Что делаем мы. Проводим объём через договор купли-продажи, заводим в государственную систему учёта, выдаём электронный документ на каждую машину и QR код для поста. Декларацию и отчёт за период готовим, если они нужны.&lt;br&gt;Работаем от маленькой делянки до партий в сотни кубов, с ИП, организациями и частными лицами.&lt;br&gt;Не хотите искать покупателя, поможем реализовать через свой оптовый канал.&lt;br&gt;Пришлите породу и объём, ответим в течение дня.&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, дрова.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/sd_overgrown.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d04.jpg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Костромская обл., Буй, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>2026-10-01T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>2026-09-01T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4535216887</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна ель(эсд на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Архангельская область, пиловочник сосна и ель с расчистки поля.&lt;br&gt; &lt;br&gt;Делаю ЭСД на вывоз леса. Расшифровка простая, электронная накладная, которую сейчас требуют на каждую машину с древесиной. Оформление идёт в государственной ФГИС ЛК, у меня уходит около пятнадцати минут.&lt;br&gt; &lt;br&gt;Если лес взят с сельхозугодий и документов на него нет вообще, тоже помогу. Провожу объём через договор купли-продажи и завожу в систему, дальше на него уже выпускаются накладные.&lt;br&gt; &lt;br&gt;Работаем так: даёте данные машины и водителя, породу и кубатуру, маршрут. Я завожу рейс в систему и отправляю готовый документ с QR-кодом. Напишите, обсудим.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl15.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j03.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j04.jpg</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Архангельская обл., Шенкурск, ул. Ленина, 8</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>3200</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>2026-09-02T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>5028333172</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ель баланс, QR код и документы на перевозку</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Делаем документы на вывоз еловых балансов и другого леса с сельхозугодий.&lt;br&gt;Главная боль тут простая: машина гружёная, ехать надо, а бумаг на груз нет. Останавливают на посту и начинается разбирательство.&lt;br&gt;Мы это закрываем. На каждый рейс выпускаем электронный сопроводительный документ и QR код: водитель показывает код, инспектор сканирует, видит откуда груз и пропускает. Плюс заводим сам объём в государственную систему, без этого документы на перевозку просто не выпустить.&lt;br&gt;Подходит и под разовую вывозку, и под постоянную отгрузку по графику.&lt;br&gt;Отдельно помогаем со сбытом, сами работаем оптом по лесу.&lt;br&gt;Напишите породу, кубатуру и маршрут, ответим быстро.&lt;br&gt;Ель баланс, пиловочник, кругляк, дрова.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s04.jpg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Ленинградская обл., Сланцы, ул. Ленина, 10</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>2026-10-02T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>2026-09-02T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2416556708</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Кругляк с лесополосы, документы под ключ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Оформляем документы на кругляк, срубленный при расчистке лесополосы или заросшего края поля.&lt;br&gt;Такие посадки чистят каждый год, древесина получается вполне товарная, но по учёту она нигде не проходит. Из-за этого её нельзя ни легально вывезти, ни продать на комбинат.&lt;br&gt;Как решаем. Заводим объём в государственную систему учёта древесины через договор купли-продажи, дальше выдаём сопроводительный документ на каждую машину и QR код, который проверяют на посту. При необходимости готовим декларацию и годовую отчётность.&lt;br&gt;Работаем и с одной машиной, и с партией в несколько сотен кубов.&lt;br&gt;Продавать самим не обязательно, у нас свой оптовый канал, можем выкупить объём.&lt;br&gt;Пришлите породу и примерную кубатуру, посчитаем сроки и цену.&lt;br&gt;Кругляк, пиловочник, сосна, ель, деловая древесина.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/nb_windbreak_logs.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s07.jpg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Валдай, ул. Ленина, 12</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>2026-10-02T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>2026-09-02T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>6582336083</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Кругляк хвойный, документы и QR на вывозку</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Оформляем документы на хвойный кругляк, срубленный на сельхозземле, чтобы его можно было законно вывезти и продать.&lt;br&gt;Ситуация знакомая: лес свален у края поля, покупатель есть, а бумаг на древесину нет ни одной. Возить так рискованно, продать юрлицу тоже не выйдет.&lt;br&gt;Что мы делаем. Проводим ваш объём через договор купли-продажи от собственного леса и заводим в государственную систему учёта. После этого выпускаем электронный документ на каждую машину и QR код, который сканируют на посту.&lt;br&gt;Отчётность за период тоже закроем, если она вам нужна.&lt;br&gt;Работаем удалённо, приезжать никуда не надо. Если объём девать некуда, забираем себе, торгуем лесом оптом.&lt;br&gt;Напишите породу и кубатуру, посчитаем в тот же день.&lt;br&gt;Кругляк хвойный, сосна, ель, пиловочник, деловая древесина.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/field_windbreak.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s09.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d07.jpg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Сольцы, ул. Ленина, 8</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7597641417</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Сосна деловая, документы на вывоз и продажу</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Оформляем документы на деловую сосну со старых лесополос и сельхозземель, чтобы её можно было законно вывезти и продать.&lt;br&gt;После расчистки края поля остаётся хороший деловой лес, но продать его не выйдет: покупатель попросит документы, а их нет.&lt;br&gt;Как это чинится. Проводим объём через договор купли-продажи и заводим в государственную систему учёта. Дальше выпускаем документ на каждую машину и QR код для поста, готовим декларацию и годовой отчёт, подбираем коды на продукцию для юрлиц.&lt;br&gt;Берём и небольшие партии, и объёмы в сотни кубов, работаем по всей стране удалённо.&lt;br&gt;Продавать самим не обязательно, у нас свой опт, можем взять реализацию на себя.&lt;br&gt;Пришлите породу и кубатуру, посчитаем стоимость.&lt;br&gt;Сосна деловая, кругляк, пиловочник, ель, баланс.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d06.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p06.jpg</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Елец, ул. Ленина, 26</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>2026-09-03T05:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9397264420</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Берёза кругляк дрова(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Кировская область, берёза кругляком, дрова и баланс с зарастающего поля.&lt;br&gt; &lt;br&gt;По документам закрываю перевозку. Каждой машине сейчас нужен QR-код на рейс, без него лес не увезти. Делаю его в ФГИС ЛК, это та самая государственная система учёта древесины, документ настоящий и на весовой вопросов не вызывает.&lt;br&gt; &lt;br&gt;Берёза с брошенной пашни идёт и на дрова, и на баланс для комбината, но и там, и там попросят бумаги на происхождение. Оформляю их с нуля.&lt;br&gt; &lt;br&gt;От вас номер машины, порода и объём, маршрут от делянки до места. Через пятнадцать минут скидываю готовое. Пишите.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl16.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j06.jpg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Кировская обл., Малмыж, ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>2026-09-03T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2149301607</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, лесополоса, документы на лес</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Оформляем документы на сосновый кругляк с полезащитных лесополос.&lt;br&gt;Таких посадок по стране очень много, их регулярно чистят и обновляют, а срубленное потом лежит без движения, потому что учёта древесины никто не вёл.&lt;br&gt;Мы делаем так. Заводим ваш объём в государственную систему через договор купли-продажи, дальше выпускаем сопроводительный документ на каждую машину и QR код для проверки на дороге. Отчётность за период тоже закрываем.&lt;br&gt;Работаем с фермерскими хозяйствами, сельхозпредприятиями, ИП и подрядчиками на расчистке.&lt;br&gt;Есть свой оптовый канал, можем забрать объём сами, если так проще.&lt;br&gt;Напишите породу и кубатуру, посчитаем сроки оформления.&lt;br&gt;Сосна кругляк, пиловочник, лесополоса, дрова.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s08.jpg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Орловская обл., Ливны, ул. Ленина, 30</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>2026-10-03T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>2026-09-03T13:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9250705504</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Кругляк ель сосна(учёт и документы фгис)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ярославская область, кругляк ель и сосна с расчистки сельхозугодий.&lt;br&gt; &lt;br&gt;Веду учёт древесины и делаю документы. Завожу объём в ФГИС ЛК, дальше выпускаю накладную на каждую машину и QR-код на рейс. Если нужна отчётность за период, декларацию и годовой отчёт тоже закрываю.&lt;br&gt; &lt;br&gt;Часто приходят с тем, что лес уже срублен, лежит, а бумаг нет. Это решается: провожу объём через договор купли-продажи, и древесина появляется в системе законно.&lt;br&gt; &lt;br&gt;Работаю удалённо со всеми регионами. От вас порода, кубатура и участок. Пишите.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl18.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j09.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j10.jpg</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Ярославская обл., Мышкин, Успенская пл., 4</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>2026-09-04T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -23571,7 +25641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -25742,6 +27812,256 @@
       <c r="AC18" t="inlineStr">
         <is>
           <t>2026-08-17T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1554853888</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl17.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j07.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j08.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>320</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Лес кругляк хвоя(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Оформляю документы на лес в ФГИС ЛК. Объясню по-простому, как это устроено.&lt;br&gt;&lt;br&gt;По закону каждая машина с древесиной идёт с электронным сопроводительным документом. Нет документа: на посту рейс останавливают, дальше простой и разбирательство.&lt;br&gt;&lt;br&gt;Как работаем:&lt;br&gt;1. Вы скидываете данные: порода, кубатура, номер машины, откуда и куда рейс.&lt;br&gt;2. Я формирую документ в системе.&lt;br&gt;3. Водителю уходит QR-код, он показывает его с телефона при проверке.&lt;br&gt;&lt;br&gt;Отдельно беру объёмы с сельхозземли и лесополос, у которых бумаг не было никогда. Хвоя, листва, кругляк, пиловочник, дрова: оформляю всё. Любой регион, работаю без выходных.&lt;br&gt;&lt;br&gt;Пишите, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Устюжна, Советская ул., 25</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-10-01T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-09-01T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4209323466</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s06.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>300</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Документы на кругляк и пиломатериалы, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Оформляем документы на кругляк и пиломатериалы, включая лес, срубленный на сельхозземле.&lt;br&gt;Что именно закрываем. Заводим объём в государственную систему учёта древесины, готовим электронный документ на каждую перевозку, QR код для проверки на посту, лесную декларацию, годовую отчётность и коды на продукцию, которые просят покупатели-юрлица.&lt;br&gt;Отдельно разбираем ситуации, когда лес взят со старой обсадки вокруг хозяйства или с края поля и по бумагам нигде не числится.&lt;br&gt;Работаем удалённо по всем регионам, с организациями, ИП и частниками. Помогаем и тем, кто только начинает, и тем, у кого партия уже застряла в пути.&lt;br&gt;Нужно ещё и продать объём, подскажем как, торгуем лесом сами.&lt;br&gt;Опишите ситуацию в сообщении, разберём бесплатно.&lt;br&gt;Кругляк, пиломатериалы, пиловочник, доска, брус.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Кирсанов, ул. Ленина, 18</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-10-02T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-09-02T12:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -1871,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -1998,6 +1998,11 @@
         </is>
       </c>
       <c r="V2" s="7" t="n"/>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -2267,6 +2272,11 @@
       <c r="U5" t="inlineStr">
         <is>
           <t>2026-07-31T09:40:50+03:00</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -2661,6 +2671,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -2907,6 +2922,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2999,6 +3019,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3091,6 +3116,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3183,6 +3213,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3275,6 +3310,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3367,6 +3407,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3459,6 +3504,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3551,6 +3601,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3643,6 +3698,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3735,6 +3795,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3827,6 +3892,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3919,6 +3989,11 @@
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4004,6 +4079,11 @@
           <t>2026-07-21T20:00:00+03:00</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4089,6 +4169,11 @@
           <t>2026-07-23T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:37:38+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4172,6 +4257,11 @@
       <c r="T19" t="inlineStr">
         <is>
           <t>2026-07-24T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -4722,6 +4812,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -5106,6 +5201,11 @@
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-06T17:36:41+03:00</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -5247,6 +5347,11 @@
           <t>2026-07-30T14:38:40+03:00</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5386,6 +5491,11 @@
           <t>2026-07-30T05:36:10+03:00</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5518,6 +5628,11 @@
           <t>2026-08-05T14:07:50+03:00</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5648,6 +5763,11 @@
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-06T08:09:57+03:00</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -5789,6 +5909,11 @@
           <t>2026-07-31T10:52:09+03:00</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5933,6 +6058,11 @@
           <t>2026-07-29T11:26:08+03:00</t>
         </is>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6072,6 +6202,11 @@
           <t>2026-08-02T09:09:41+03:00</t>
         </is>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6211,6 +6346,11 @@
           <t>2026-07-31T08:09:38+03:00</t>
         </is>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6343,6 +6483,11 @@
           <t>2026-08-06T13:37:50+03:00</t>
         </is>
       </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6475,6 +6620,11 @@
           <t>2026-08-05T10:10:53+03:00</t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6600,6 +6750,11 @@
           <t>2026-07-22T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2026-09-20T12:36:07+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6725,6 +6880,11 @@
           <t>2026-07-25T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:37:51+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6850,6 +7010,11 @@
           <t>2026-07-25T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2026-09-23T15:09:35+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6975,6 +7140,11 @@
           <t>2026-08-06T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2026-09-05T16:07:37+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7100,6 +7270,11 @@
           <t>2026-08-07T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2026-09-06T06:06:05+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7225,6 +7400,11 @@
           <t>2026-08-08T04:30:00+03:00</t>
         </is>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2026-09-07T04:35:41+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7350,6 +7530,11 @@
           <t>2026-08-13T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2026-09-12T18:06:07+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7475,6 +7660,11 @@
           <t>2026-08-15T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:38:14+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7600,6 +7790,11 @@
           <t>2026-08-16T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2026-09-15T18:06:23+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7725,6 +7920,11 @@
           <t>2026-09-03T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7848,6 +8048,11 @@
       <c r="AD26" t="inlineStr">
         <is>
           <t>2026-09-03T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2026-10-03T13:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ119"/>
+  <dimension ref="A1:AK119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -8706,6 +8911,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AK2" s="7" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -9149,6 +9359,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9286,6 +9501,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9423,6 +9643,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9560,6 +9785,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9697,6 +9927,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9834,6 +10069,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9971,6 +10211,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10108,6 +10353,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10245,6 +10495,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10382,6 +10637,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10519,6 +10779,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10656,6 +10921,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10793,6 +11063,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10930,6 +11205,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11067,6 +11347,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11204,6 +11489,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11341,6 +11631,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11478,6 +11773,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11615,6 +11915,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11752,6 +12057,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11889,6 +12199,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12026,6 +12341,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12163,6 +12483,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12300,6 +12625,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12437,6 +12767,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12574,6 +12909,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12711,6 +13051,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12848,6 +13193,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12985,6 +13335,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13122,6 +13477,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13259,6 +13619,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13396,6 +13761,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13533,6 +13903,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13670,6 +14045,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13807,6 +14187,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13944,6 +14329,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14081,6 +14471,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14218,6 +14613,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14343,6 +14743,11 @@
           <t>не опт</t>
         </is>
       </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14473,6 +14878,11 @@
           <t>2026-07-15T16:33:49+03:00</t>
         </is>
       </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-09-13T17:37:02+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14603,6 +15013,11 @@
           <t>2026-07-16T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-09-14T05:36:45+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14733,6 +15148,11 @@
           <t>2026-07-16T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-09-14T08:08:02+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14863,6 +15283,11 @@
           <t>2026-07-16T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:38:08+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14993,6 +15418,11 @@
           <t>2026-07-16T12:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-09-14T13:07:14+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15123,6 +15553,11 @@
           <t>2026-07-16T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:37:12+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15253,6 +15688,11 @@
           <t>2026-07-16T17:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-09-14T18:06:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15383,6 +15823,11 @@
           <t>2026-07-16T20:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:35:57+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15513,6 +15958,11 @@
           <t>2026-07-17T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-09-15T05:35:43+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15643,6 +16093,11 @@
           <t>2026-07-17T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2026-09-15T07:37:05+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15773,6 +16228,11 @@
           <t>2026-07-17T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-09-15T10:37:30+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15903,6 +16363,11 @@
           <t>2026-07-17T12:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:07:04+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16033,6 +16498,11 @@
           <t>2026-07-17T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2026-09-15T15:36:34+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16163,6 +16633,11 @@
           <t>2026-07-17T17:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2026-09-15T18:06:23+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16293,6 +16768,11 @@
           <t>2026-07-17T20:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>2026-09-15T20:36:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16419,6 +16899,11 @@
           <t>2026-07-21T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>2026-09-19T15:37:38+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16545,6 +17030,11 @@
           <t>2026-07-21T17:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16671,6 +17161,11 @@
           <t>2026-07-22T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16797,6 +17292,11 @@
           <t>2026-07-22T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:36:02+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16923,6 +17423,11 @@
           <t>2026-07-22T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>2026-09-20T15:08:18+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17049,6 +17554,11 @@
           <t>2026-07-22T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:37:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17175,6 +17685,11 @@
           <t>2026-07-23T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>2026-09-21T06:35:34+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17301,6 +17816,11 @@
           <t>2026-07-23T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:37:22+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17427,6 +17947,11 @@
           <t>2026-07-23T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17553,6 +18078,11 @@
           <t>2026-07-24T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:35:56+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17679,6 +18209,11 @@
           <t>2026-07-24T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:37:13+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17805,6 +18340,11 @@
           <t>2026-07-24T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:37:09+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17931,6 +18471,11 @@
           <t>2026-07-25T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>2026-09-23T06:35:57+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18055,6 +18600,11 @@
       <c r="AJ72" t="inlineStr">
         <is>
           <t>2026-07-25T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:37:29+03:00</t>
         </is>
       </c>
     </row>
@@ -18191,6 +18741,11 @@
           <t>2026-07-29T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2026-09-27T15:39:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18325,6 +18880,11 @@
           <t>2026-07-29T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>2026-09-27T15:39:48+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18459,6 +19019,11 @@
           <t>2026-07-29T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>2026-09-27T19:06:59+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18593,6 +19158,11 @@
           <t>2026-07-29T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18725,6 +19295,11 @@
       <c r="AJ77" t="inlineStr">
         <is>
           <t>2026-07-30T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>2026-09-28T06:36:14+03:00</t>
         </is>
       </c>
     </row>
@@ -18862,6 +19437,11 @@
           <t>2026-07-30T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>2026-09-28T10:37:31+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18996,6 +19576,11 @@
           <t>2026-07-30T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:37:20+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -19130,6 +19715,11 @@
           <t>2026-07-30T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2026-09-28T18:36:26+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19262,6 +19852,11 @@
       <c r="AJ81" t="inlineStr">
         <is>
           <t>2026-07-31T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2026-09-29T06:36:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19399,6 +19994,11 @@
           <t>2026-07-31T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:06:26+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -19534,6 +20134,11 @@
           <t>2026-07-31T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:06:25+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19668,6 +20273,11 @@
           <t>2026-07-31T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:36:38+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19800,6 +20410,11 @@
       <c r="AJ85" t="inlineStr">
         <is>
           <t>2026-08-01T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>2026-09-30T06:39:32+03:00</t>
         </is>
       </c>
     </row>
@@ -19937,6 +20552,11 @@
           <t>2026-08-01T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2026-09-30T10:43:23+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -20072,6 +20692,11 @@
           <t>2026-08-01T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:08:32+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -20207,6 +20832,11 @@
           <t>2026-08-01T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:37:04+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -20342,6 +20972,11 @@
           <t>2026-07-28T13:15:00+03:00</t>
         </is>
       </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2026-09-26T14:38:23+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20477,6 +21112,11 @@
           <t>2026-07-28T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20607,6 +21247,11 @@
           <t>2026-08-06T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2026-09-19T16:06:27+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -20737,6 +21382,11 @@
           <t>2026-08-07T04:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -20867,6 +21517,11 @@
           <t>2026-08-07T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2026-09-06T07:36:37+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -20997,6 +21652,11 @@
           <t>2026-08-08T03:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:05:22+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -21127,6 +21787,11 @@
           <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -21257,6 +21922,11 @@
           <t>2026-08-13T16:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2026-09-12T16:07:34+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -21387,6 +22057,11 @@
           <t>2026-08-14T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2026-09-13T06:05:59+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -21517,6 +22192,11 @@
           <t>2026-08-14T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2026-09-13T08:07:57+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -21647,6 +22327,11 @@
           <t>2026-08-14T17:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2026-09-13T17:37:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -21777,6 +22462,11 @@
           <t>2026-08-15T05:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -21907,6 +22597,11 @@
           <t>2026-08-15T09:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>2026-09-14T09:37:09+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22037,6 +22732,11 @@
           <t>2026-08-15T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2026-09-14T12:07:28+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22167,6 +22867,11 @@
           <t>2026-08-16T08:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -22297,6 +23002,11 @@
           <t>2026-08-16T11:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -22427,6 +23137,11 @@
           <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -22557,6 +23272,11 @@
           <t>2026-08-31T16:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:30:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -22687,6 +23407,11 @@
           <t>2026-08-31T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -22817,6 +23542,11 @@
           <t>2026-09-01T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22947,6 +23677,11 @@
           <t>2026-09-01T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>2026-10-01T04:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -23077,6 +23812,11 @@
           <t>2026-09-01T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>2026-10-01T06:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -23207,6 +23947,11 @@
           <t>2026-09-01T11:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>2026-10-01T08:30:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -23337,6 +24082,11 @@
           <t>2026-09-02T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -23467,6 +24217,11 @@
           <t>2026-09-02T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>2026-10-02T04:30:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23597,6 +24352,11 @@
           <t>2026-09-02T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>2026-10-02T07:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23727,6 +24487,11 @@
           <t>2026-09-02T15:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -23857,6 +24622,11 @@
           <t>2026-09-03T05:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:30:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23987,6 +24757,11 @@
           <t>2026-09-03T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:30:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -24117,6 +24892,11 @@
           <t>2026-09-03T13:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>2026-10-03T10:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24245,6 +25025,11 @@
       <c r="AJ119" t="inlineStr">
         <is>
           <t>2026-09-04T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -25641,7 +26426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -25803,6 +26588,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -26184,6 +26974,11 @@
           <t>2026-08-02T21:06:52+03:00</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26311,6 +27106,11 @@
           <t>2026-08-06T11:37:58+03:00</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26438,6 +27238,11 @@
           <t>2026-07-31T11:37:05+03:00</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26575,6 +27380,11 @@
           <t>2026-07-31T12:37:11+03:00</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26702,6 +27512,11 @@
           <t>2026-08-05T16:06:16+03:00</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26829,6 +27644,11 @@
           <t>2026-08-06T06:42:07+03:00</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26949,6 +27769,11 @@
           <t>2026-07-23T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-09-21T18:36:36+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27069,6 +27894,11 @@
           <t>2026-07-24T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:36:26+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27189,6 +28019,11 @@
           <t>2026-07-25T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:37:01+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27314,6 +28149,11 @@
           <t>2026-08-07T03:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2026-09-06T03:06:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27439,6 +28279,11 @@
           <t>2026-08-07T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2026-09-06T09:08:27+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27564,6 +28409,11 @@
           <t>2026-08-14T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026-09-13T10:38:24+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27689,6 +28539,11 @@
           <t>2026-08-16T06:30:00+03:00</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026-09-15T06:35:46+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27814,6 +28669,11 @@
           <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2026-09-16T09:07:40+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27939,6 +28799,11 @@
           <t>2026-09-01T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2026-10-01T11:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -28062,6 +28927,11 @@
       <c r="AC20" t="inlineStr">
         <is>
           <t>2026-09-02T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-10-02T09:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -8053,6 +8053,396 @@
       <c r="AE26" t="inlineStr">
         <is>
           <t>2026-10-03T13:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4788141290</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl16.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s03.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d03.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>350</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Документы на срубленный лес, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Лес срублен, лежит, а по бумагам его нет. Значит ни продать, ни вывезти.&lt;br&gt;Разбираем такую ситуацию с нуля. Смотрим, откуда объём и чей участок, готовим договор купли-продажи от своего леса, заводим древесину в государственную систему учёта. После этого объём существует официально.&lt;br&gt;На руки отдаём весь пакет: электронный документ на каждый рейс, QR код для проверки на посту, коды продукции для покупателя, отчётность за период, если она нужна.&lt;br&gt;Работаем удалённо по всей стране, приезжать никуда не надо. От вас порода, кубатура и адрес участка.&lt;br&gt;Если продавать самим некогда, забираем объём себе, работаем оптом по лесу.&lt;br&gt;Напишите в сообщения, разберём вашу ситуацию бесплатно.&lt;br&gt;Сосна, ель, берёза, осина, кругляк, пиловочник, баланс, ФГИС ЛК, ЭСД, QR код.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Кировская обл., Уржум, ул. Советская, 25</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-10-10T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2026-09-10T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2026-10-10T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8206612593</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/logs_close.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j06.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s09.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>350</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Отчётность в ФГИС ЛК, декларация и 1-ИЛ</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Подходит срок сдачи, а отчётность в системе не собрана. Берём это на себя.&lt;br&gt;Сдаём лесную декларацию по вашим сделкам, годовой отчёт об использовании лесов, ведём складской учёт и движение остатков. Если в системе уже накопились расхождения по объёмам, сначала приводим учёт в норму, потом сдаём.&lt;br&gt;Работаем по вашим данным удалённо, подпись и доступ остаются у вас.&lt;br&gt;Параллельно закрываем текущие перевозки: документ на рейс и код, который сканируют на дороге.&lt;br&gt;Отдельная история, когда древесина есть, а происхождения в бумагах нет. Такой объём проводим через договор купли-продажи и заводим в учёт официально.&lt;br&gt;Первый разбор ситуации бесплатный, скажите, что у вас за период и по каким сделкам.&lt;br&gt;МСД, ОЛИ, 1-ИЛ, лесная декларация, складской учёт, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Республика Коми, Печора, ул. Ленинградская, 15</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026-10-10T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>2026-09-10T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2026-10-10T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7730111798</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl15.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d07.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p07.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>350</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Документы на лес с поля и лесополосы</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Расчистили поле или старую лесополосу, древесина лежит, а девать её некуда: без бумаг не берёт ни один покупатель.&lt;br&gt;Учёт древесины одинаков для любой земли. Участок ваш, но объём всё равно надо провести официально. Делаем это через договор купли-продажи и запись в государственную систему, дальше выдаём документы на вывоз.&lt;br&gt;Срок давности заготовки роли не играет, оформляем и то, что срублено в прошлом сезоне.&lt;br&gt;Берём расчистку под пашню, спил старой лесополосы, самосев на брошенном поле.&lt;br&gt;Если продавать самим некогда, забираем партию через свой оптовый канал, оцениваем по породе и сортименту.&lt;br&gt;Пришлите фото участка и примерный объём на глаз, дальше считаем сами.&lt;br&gt;Берёза, осина, сосна, дрова, баланс, ЭСД, QR код, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Архангельская обл., Плесецк, ул. Ленина, 21</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2026-09-10T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -26426,7 +26816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -28932,6 +29322,266 @@
       <c r="AD20" t="inlineStr">
         <is>
           <t>2026-10-02T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2088776918</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl18.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_j01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s04.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>350</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на перевозку леса, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Машина под погрузкой, а документа на груз нет. Оформляем электронный сопроводительный документ и QR код на конкретный рейс.&lt;br&gt;Что нужно от вас: номер машины и данные водителя, порода и кубатура груза, маршрут откуда и куда. Обычно укладываемся минут в пятнадцать, срочный рейс закрываем первым.&lt;br&gt;Если объёма нет в системе вообще, сначала заводим его туда через договор купли-продажи от своего леса, а дальше выпускаем накладные на каждую машину.&lt;br&gt;Возите регулярно, ведём постоянно, документы под каждый рейс без простоев.&lt;br&gt;На посту инспектор сканирует код и видит, откуда груз. Проверка занимает у него меньше минуты.&lt;br&gt;Скажите, когда выезд, успеем к погрузке.&lt;br&gt;Кругляк, пиломатериал, дрова, баланс, ЭСД, QR код, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Крестцы, ул. Московская, 24</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-10-10T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-10-10T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8372293443</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl14.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s01.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>350</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Документы на лес для продажи юрлицу</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Покупатель готов забрать древесину, но просит документы, а их нет. Собираем пакет, который спокойно примет бухгалтерия комбината.&lt;br&gt;Готовим подтверждение происхождения, накладную на груз, коды продукции ОКПД2 на товар, электронный документ и код на каждую машину. Для юрлица и для тендера этого обычно достаточно.&lt;br&gt;Если объём вообще не заведён в систему учёта, начинаем с него: договор купли-продажи от своего леса и запись в ФГИС ЛК.&lt;br&gt;Сроки короткие. Документы на перевозку делаем в день обращения, учёт объёма обычно за один рабочий день.&lt;br&gt;Скажите породу, сортимент и куда идёт машина, посчитаем в тот же день.&lt;br&gt;Пиловочник, баланс, фанкряж, дрова, ОКПД2, ЭСД, QR код, ФГИС ЛК.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Питкяранта, ул. Ленина, 43</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-10-10T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-09-10T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2026-10-10T12:30:00+03:00</t>
         </is>
       </c>
     </row>
